--- a/data/shadow/informe_bot.xlsx
+++ b/data/shadow/informe_bot.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0000 &quot;€&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,12 +105,6 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00212121"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00283593"/>
       <sz val="10"/>
     </font>
     <font>
@@ -215,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,19 +277,19 @@
     <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -316,15 +310,6 @@
     <xf numFmtId="165" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -334,10 +319,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -363,9 +348,6 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -497,7 +479,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$21:$B$84</f>
+              <f>'Dashboard'!$B$21:$B$102</f>
             </numRef>
           </val>
         </ser>
@@ -867,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -889,7 +871,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actualizado: 24/06/2026 08:11 UTC</t>
+          <t>Actualizado: 24/06/2026 10:29 UTC</t>
         </is>
       </c>
     </row>
@@ -990,7 +972,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -1010,7 +992,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1013,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>29 / 35</t>
+          <t>35 / 47</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1053,7 +1035,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1075,7 +1057,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>-6.86 €</t>
+          <t>-12.63 €</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1097,7 +1079,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1119,7 +1101,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1141,7 +1123,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>13.14 €</t>
+          <t>7.37 €</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1163,7 +1145,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>❌ × 1</t>
+          <t>❌ × 6</t>
         </is>
       </c>
     </row>
@@ -1696,6 +1678,150 @@
       </c>
       <c r="B84" t="n">
         <v>13.1393</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>65</v>
+      </c>
+      <c r="B85" t="n">
+        <v>14.0395</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>66</v>
+      </c>
+      <c r="B86" t="n">
+        <v>13.1215</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>67</v>
+      </c>
+      <c r="B87" t="n">
+        <v>14.0785</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>68</v>
+      </c>
+      <c r="B88" t="n">
+        <v>13.1605</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>69</v>
+      </c>
+      <c r="B89" t="n">
+        <v>12.2425</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>70</v>
+      </c>
+      <c r="B90" t="n">
+        <v>11.3245</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>71</v>
+      </c>
+      <c r="B91" t="n">
+        <v>12.1887</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>72</v>
+      </c>
+      <c r="B92" t="n">
+        <v>13.0889</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>73</v>
+      </c>
+      <c r="B93" t="n">
+        <v>12.1709</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>74</v>
+      </c>
+      <c r="B94" t="n">
+        <v>11.2529</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>75</v>
+      </c>
+      <c r="B95" t="n">
+        <v>12.0825</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>76</v>
+      </c>
+      <c r="B96" t="n">
+        <v>12.8788</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>77</v>
+      </c>
+      <c r="B97" t="n">
+        <v>11.9608</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>78</v>
+      </c>
+      <c r="B98" t="n">
+        <v>11.0428</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>79</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10.1248</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>80</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9.206799999999999</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>81</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8.2888</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>82</v>
+      </c>
+      <c r="B102" t="n">
+        <v>7.3708</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1888,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1772,7 +1898,7 @@
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>+0.8714 €</t>
+          <t>+0.8719 €</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1910,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1806,7 +1932,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>-6.86 €</t>
+          <t>-12.63 €</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1816,7 +1942,7 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>10.53 €</t>
+          <t>15.28 €</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1954,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>-0.1072 €</t>
+          <t>-0.1540 €</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1838,7 +1964,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>-0.118</t>
+          <t>-0.171</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1976,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1860,7 +1986,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>-0.65x</t>
+          <t>-0.83x</t>
         </is>
       </c>
     </row>
@@ -1955,28 +2081,28 @@
         </is>
       </c>
       <c r="B12" s="20" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>0.54</v>
+        <v>0.5185</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>0.0385</v>
+        <v>0.0179</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>1.7169</v>
+        <v>-0.1369</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>0.0343</v>
+        <v>-0.0025</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.0343</v>
+        <v>-0.0025</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>1.0813</v>
+        <v>0.9943</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>5</v>
@@ -1985,13 +2111,13 @@
         <v>4</v>
       </c>
       <c r="L12" s="26" t="n">
-        <v>0.0125</v>
+        <v>0.0154</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>0.0382</v>
+        <v>-0.0028</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="O12" s="29" t="inlineStr">
         <is>
@@ -2006,52 +2132,52 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C13" s="31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="32" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>-0.3333</v>
-      </c>
-      <c r="F13" s="34" t="n">
-        <v>-3.672</v>
-      </c>
-      <c r="G13" s="34" t="n">
-        <v>-0.918</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>-0.918</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>0</v>
+        <v>-0.2857</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-6.7416</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>-0.5618</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>-0.5618</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0.2656</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="37" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M13" s="38" t="n">
-        <v>-1.02</v>
+        <v>5</v>
+      </c>
+      <c r="L13" s="34" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="M13" s="35" t="n">
+        <v>-0.6242</v>
       </c>
       <c r="N13" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="39" t="inlineStr">
+      <c r="O13" s="36" t="inlineStr">
         <is>
           <t>TIMING_CORTO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>💡  Profit Factor &gt;1.5 = buena estrategia  |  Expectancy &gt;0 = edge real  |  Kelly Opt. = fracción óptima de bankroll a arriesgar por operación  |  IC Bayes = información real que aporta la estrategia (&gt;0.05 = útil)</t>
         </is>
@@ -2172,7 +2298,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>⏳ Sin operaciones reales todavía. Se registrarán aquí cuando el bot esté activo.</t>
         </is>
@@ -2230,7 +2356,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>💡 Añade tu depósito inicial en data/live/bankroll.csv para empezar el tracking.</t>
         </is>
@@ -2250,7 +2376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2348,7 +2474,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E2" s="42" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:30AM-1:35AM ET</t>
         </is>
@@ -2358,7 +2484,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G2" s="43" t="n">
+      <c r="G2" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H2" s="20" t="inlineStr">
@@ -2371,13 +2497,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J2" s="44" t="n">
+      <c r="J2" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K2" s="44" t="n">
+      <c r="K2" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L2" s="45" t="n">
+      <c r="L2" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -2400,7 +2526,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E3" s="46" t="inlineStr">
+      <c r="E3" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 1:30AM-1:35AM ET</t>
         </is>
@@ -2410,7 +2536,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G3" s="47" t="n">
+      <c r="G3" s="44" t="n">
         <v>0.48</v>
       </c>
       <c r="H3" s="31" t="inlineStr">
@@ -2423,13 +2549,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J3" s="44" t="n">
+      <c r="J3" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K3" s="44" t="n">
+      <c r="K3" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L3" s="45" t="n">
+      <c r="L3" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -2452,7 +2578,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1:35AM-1:40AM ET</t>
         </is>
@@ -2462,7 +2588,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G4" s="43" t="n">
+      <c r="G4" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H4" s="20" t="inlineStr">
@@ -2475,13 +2601,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J4" s="44" t="n">
+      <c r="J4" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K4" s="44" t="n">
+      <c r="K4" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L4" s="45" t="n">
+      <c r="L4" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -2504,7 +2630,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E5" s="46" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:35AM-1:40AM ET</t>
         </is>
@@ -2514,7 +2640,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G5" s="47" t="n">
+      <c r="G5" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H5" s="31" t="inlineStr">
@@ -2527,13 +2653,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J5" s="48" t="n">
+      <c r="J5" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K5" s="48" t="n">
+      <c r="K5" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L5" s="49" t="n">
+      <c r="L5" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -2556,7 +2682,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 1:35AM-1:40AM ET</t>
         </is>
@@ -2566,7 +2692,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="40" t="n">
         <v>0.485</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -2579,13 +2705,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J6" s="48" t="n">
+      <c r="J6" s="45" t="n">
         <v>0.9557</v>
       </c>
-      <c r="K6" s="48" t="n">
+      <c r="K6" s="45" t="n">
         <v>0.9377</v>
       </c>
-      <c r="L6" s="49" t="n">
+      <c r="L6" s="46" t="n">
         <v>1.041888888888889</v>
       </c>
     </row>
@@ -2608,7 +2734,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:30AM-1:45AM ET</t>
         </is>
@@ -2618,7 +2744,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H7" s="31" t="inlineStr">
@@ -2631,13 +2757,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J7" s="48" t="n">
+      <c r="J7" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L7" s="49" t="n">
+      <c r="L7" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -2660,7 +2786,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>XRP Up or Down - June 24, 1:30AM-1:45AM ET</t>
         </is>
@@ -2670,7 +2796,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G8" s="43" t="n">
+      <c r="G8" s="40" t="n">
         <v>0.48</v>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -2683,13 +2809,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J8" s="48" t="n">
+      <c r="J8" s="45" t="n">
         <v>0.975</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="45" t="n">
         <v>0.957</v>
       </c>
-      <c r="L8" s="49" t="n">
+      <c r="L8" s="46" t="n">
         <v>1.063333333333333</v>
       </c>
     </row>
@@ -2712,7 +2838,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1:30AM-1:45AM ET</t>
         </is>
@@ -2722,7 +2848,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="44" t="n">
         <v>0.475</v>
       </c>
       <c r="H9" s="31" t="inlineStr">
@@ -2735,13 +2861,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J9" s="48" t="n">
+      <c r="J9" s="45" t="n">
         <v>0.9947</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="45" t="n">
         <v>0.9767</v>
       </c>
-      <c r="L9" s="49" t="n">
+      <c r="L9" s="46" t="n">
         <v>1.085222222222222</v>
       </c>
     </row>
@@ -2764,7 +2890,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E10" s="42" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:40AM-1:45AM ET</t>
         </is>
@@ -2774,7 +2900,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="40" t="n">
         <v>0.5</v>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -2787,13 +2913,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L10" s="45" t="n">
+      <c r="L10" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -2816,7 +2942,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 1:40AM-1:45AM ET</t>
         </is>
@@ -2826,7 +2952,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="44" t="n">
         <v>0.48</v>
       </c>
       <c r="H11" s="31" t="inlineStr">
@@ -2839,13 +2965,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J11" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K11" s="44" t="n">
+      <c r="K11" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L11" s="45" t="n">
+      <c r="L11" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -2868,7 +2994,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1:45AM-1:50AM ET</t>
         </is>
@@ -2878,7 +3004,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G12" s="43" t="n">
+      <c r="G12" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -2891,13 +3017,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J12" s="48" t="n">
+      <c r="J12" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L12" s="49" t="n">
+      <c r="L12" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -2920,7 +3046,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E13" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 1AM ET</t>
         </is>
@@ -2930,7 +3056,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="44" t="n">
         <v>0.795</v>
       </c>
       <c r="H13" s="31" t="inlineStr">
@@ -2943,13 +3069,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J13" s="44" t="n">
+      <c r="J13" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L13" s="45" t="n">
+      <c r="L13" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -2972,7 +3098,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E14" s="42" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:45AM-1:50AM ET</t>
         </is>
@@ -2982,7 +3108,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G14" s="43" t="n">
+      <c r="G14" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -2995,13 +3121,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J14" s="48" t="n">
+      <c r="J14" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K14" s="48" t="n">
+      <c r="K14" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L14" s="49" t="n">
+      <c r="L14" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -3024,7 +3150,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E15" s="46" t="inlineStr">
+      <c r="E15" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1AM ET</t>
         </is>
@@ -3034,7 +3160,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="44" t="n">
         <v>0.775</v>
       </c>
       <c r="H15" s="31" t="inlineStr">
@@ -3047,13 +3173,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J15" s="48" t="n">
+      <c r="J15" s="45" t="n">
         <v>0.2613</v>
       </c>
-      <c r="K15" s="48" t="n">
+      <c r="K15" s="45" t="n">
         <v>0.2433</v>
       </c>
-      <c r="L15" s="49" t="n">
+      <c r="L15" s="46" t="n">
         <v>0.2703333333333333</v>
       </c>
     </row>
@@ -3076,7 +3202,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E16" s="42" t="inlineStr">
+      <c r="E16" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:45AM-2:00AM ET</t>
         </is>
@@ -3086,7 +3212,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G16" s="43" t="n">
+      <c r="G16" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -3099,13 +3225,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J16" s="44" t="n">
+      <c r="J16" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K16" s="44" t="n">
+      <c r="K16" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L16" s="45" t="n">
+      <c r="L16" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3128,7 +3254,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E17" s="46" t="inlineStr">
+      <c r="E17" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:55AM-2:00AM ET</t>
         </is>
@@ -3138,7 +3264,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H17" s="31" t="inlineStr">
@@ -3151,13 +3277,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J17" s="44" t="n">
+      <c r="J17" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K17" s="44" t="n">
+      <c r="K17" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L17" s="45" t="n">
+      <c r="L17" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3180,7 +3306,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E18" s="42" t="inlineStr">
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 1:55AM-2:00AM ET</t>
         </is>
@@ -3190,7 +3316,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G18" s="43" t="n">
+      <c r="G18" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -3203,13 +3329,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J18" s="44" t="n">
+      <c r="J18" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K18" s="44" t="n">
+      <c r="K18" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L18" s="45" t="n">
+      <c r="L18" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3232,7 +3358,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E19" s="46" t="inlineStr">
+      <c r="E19" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1:55AM-2:00AM ET</t>
         </is>
@@ -3242,7 +3368,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G19" s="47" t="n">
+      <c r="G19" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H19" s="31" t="inlineStr">
@@ -3255,13 +3381,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J19" s="44" t="n">
+      <c r="J19" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K19" s="44" t="n">
+      <c r="K19" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L19" s="45" t="n">
+      <c r="L19" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3284,7 +3410,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E20" s="42" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:00AM-2:05AM ET</t>
         </is>
@@ -3294,7 +3420,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G20" s="43" t="n">
+      <c r="G20" s="40" t="n">
         <v>0.245</v>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -3307,13 +3433,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J20" s="48" t="n">
+      <c r="J20" s="45" t="n">
         <v>0.2921</v>
       </c>
-      <c r="K20" s="48" t="n">
+      <c r="K20" s="45" t="n">
         <v>0.2741</v>
       </c>
-      <c r="L20" s="49" t="n">
+      <c r="L20" s="46" t="n">
         <v>0.3045555555555556</v>
       </c>
     </row>
@@ -3336,7 +3462,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E21" s="46" t="inlineStr">
+      <c r="E21" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:05AM-2:10AM ET</t>
         </is>
@@ -3346,7 +3472,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G21" s="47" t="n">
+      <c r="G21" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H21" s="31" t="inlineStr">
@@ -3359,13 +3485,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J21" s="44" t="n">
+      <c r="J21" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K21" s="44" t="n">
+      <c r="K21" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L21" s="45" t="n">
+      <c r="L21" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3388,7 +3514,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E22" s="42" t="inlineStr">
+      <c r="E22" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:05AM-2:10AM ET</t>
         </is>
@@ -3398,7 +3524,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G22" s="43" t="n">
+      <c r="G22" s="40" t="n">
         <v>0.515</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -3411,13 +3537,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J22" s="44" t="n">
+      <c r="J22" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K22" s="44" t="n">
+      <c r="K22" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L22" s="45" t="n">
+      <c r="L22" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3440,7 +3566,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E23" s="46" t="inlineStr">
+      <c r="E23" s="43" t="inlineStr">
         <is>
           <t>Dogecoin Up or Down - June 24, 2:05AM-2:10AM ET</t>
         </is>
@@ -3450,7 +3576,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="44" t="n">
         <v>0.5</v>
       </c>
       <c r="H23" s="31" t="inlineStr">
@@ -3463,13 +3589,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J23" s="44" t="n">
+      <c r="J23" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K23" s="44" t="n">
+      <c r="K23" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L23" s="45" t="n">
+      <c r="L23" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3492,7 +3618,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E24" s="42" t="inlineStr">
+      <c r="E24" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:00AM-2:15AM ET</t>
         </is>
@@ -3502,7 +3628,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G24" s="43" t="n">
+      <c r="G24" s="40" t="n">
         <v>0.485</v>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -3515,13 +3641,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J24" s="48" t="n">
+      <c r="J24" s="45" t="n">
         <v>0.8476</v>
       </c>
-      <c r="K24" s="48" t="n">
+      <c r="K24" s="45" t="n">
         <v>0.8296</v>
       </c>
-      <c r="L24" s="49" t="n">
+      <c r="L24" s="46" t="n">
         <v>0.9217777777777778</v>
       </c>
     </row>
@@ -3544,7 +3670,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E25" s="46" t="inlineStr">
+      <c r="E25" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:00AM-2:15AM ET</t>
         </is>
@@ -3554,7 +3680,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G25" s="47" t="n">
+      <c r="G25" s="44" t="n">
         <v>0.485</v>
       </c>
       <c r="H25" s="31" t="inlineStr">
@@ -3567,13 +3693,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J25" s="48" t="n">
+      <c r="J25" s="45" t="n">
         <v>0.8476</v>
       </c>
-      <c r="K25" s="48" t="n">
+      <c r="K25" s="45" t="n">
         <v>0.8296</v>
       </c>
-      <c r="L25" s="49" t="n">
+      <c r="L25" s="46" t="n">
         <v>0.9217777777777778</v>
       </c>
     </row>
@@ -3596,7 +3722,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E26" s="42" t="inlineStr">
+      <c r="E26" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:10AM-2:15AM ET</t>
         </is>
@@ -3606,7 +3732,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G26" s="43" t="n">
+      <c r="G26" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -3619,13 +3745,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J26" s="44" t="n">
+      <c r="J26" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K26" s="44" t="n">
+      <c r="K26" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L26" s="45" t="n">
+      <c r="L26" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3648,7 +3774,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E27" s="46" t="inlineStr">
+      <c r="E27" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:15AM-2:20AM ET</t>
         </is>
@@ -3658,7 +3784,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G27" s="47" t="n">
+      <c r="G27" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H27" s="31" t="inlineStr">
@@ -3671,13 +3797,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J27" s="48" t="n">
+      <c r="J27" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K27" s="48" t="n">
+      <c r="K27" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L27" s="49" t="n">
+      <c r="L27" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -3700,7 +3826,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E28" s="42" t="inlineStr">
+      <c r="E28" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:15AM-2:20AM ET</t>
         </is>
@@ -3710,7 +3836,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G28" s="43" t="n">
+      <c r="G28" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -3723,13 +3849,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J28" s="48" t="n">
+      <c r="J28" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K28" s="48" t="n">
+      <c r="K28" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L28" s="49" t="n">
+      <c r="L28" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -3752,7 +3878,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E29" s="46" t="inlineStr">
+      <c r="E29" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:15AM-2:20AM ET</t>
         </is>
@@ -3762,7 +3888,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G29" s="47" t="n">
+      <c r="G29" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H29" s="31" t="inlineStr">
@@ -3775,13 +3901,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J29" s="48" t="n">
+      <c r="J29" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K29" s="48" t="n">
+      <c r="K29" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L29" s="49" t="n">
+      <c r="L29" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -3804,7 +3930,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E30" s="42" t="inlineStr">
+      <c r="E30" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:20AM-2:25AM ET</t>
         </is>
@@ -3814,7 +3940,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G30" s="43" t="n">
+      <c r="G30" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -3827,13 +3953,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J30" s="44" t="n">
+      <c r="J30" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K30" s="44" t="n">
+      <c r="K30" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L30" s="45" t="n">
+      <c r="L30" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -3856,7 +3982,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E31" s="46" t="inlineStr">
+      <c r="E31" s="43" t="inlineStr">
         <is>
           <t>BNB Up or Down - June 24, 2:15AM-2:30AM ET</t>
         </is>
@@ -3866,7 +3992,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G31" s="47" t="n">
+      <c r="G31" s="44" t="n">
         <v>0.475</v>
       </c>
       <c r="H31" s="31" t="inlineStr">
@@ -3879,13 +4005,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J31" s="48" t="n">
+      <c r="J31" s="45" t="n">
         <v>0.8143</v>
       </c>
-      <c r="K31" s="48" t="n">
+      <c r="K31" s="45" t="n">
         <v>0.7963</v>
       </c>
-      <c r="L31" s="49" t="n">
+      <c r="L31" s="46" t="n">
         <v>0.8847777777777778</v>
       </c>
     </row>
@@ -3908,7 +4034,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E32" s="42" t="inlineStr">
+      <c r="E32" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:15AM-2:30AM ET</t>
         </is>
@@ -3918,7 +4044,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G32" s="43" t="n">
+      <c r="G32" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -3931,13 +4057,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J32" s="48" t="n">
+      <c r="J32" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K32" s="48" t="n">
+      <c r="K32" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L32" s="49" t="n">
+      <c r="L32" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -3960,7 +4086,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E33" s="46" t="inlineStr">
+      <c r="E33" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:15AM-2:30AM ET</t>
         </is>
@@ -3970,7 +4096,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G33" s="47" t="n">
+      <c r="G33" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H33" s="31" t="inlineStr">
@@ -3983,13 +4109,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J33" s="48" t="n">
+      <c r="J33" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K33" s="48" t="n">
+      <c r="K33" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L33" s="49" t="n">
+      <c r="L33" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -4012,7 +4138,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E34" s="42" t="inlineStr">
+      <c r="E34" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:25AM-2:30AM ET</t>
         </is>
@@ -4022,7 +4148,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G34" s="43" t="n">
+      <c r="G34" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -4035,13 +4161,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J34" s="44" t="n">
+      <c r="J34" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K34" s="44" t="n">
+      <c r="K34" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L34" s="45" t="n">
+      <c r="L34" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4064,7 +4190,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E35" s="46" t="inlineStr">
+      <c r="E35" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:25AM-2:30AM ET</t>
         </is>
@@ -4074,7 +4200,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G35" s="47" t="n">
+      <c r="G35" s="44" t="n">
         <v>0.505</v>
       </c>
       <c r="H35" s="31" t="inlineStr">
@@ -4087,13 +4213,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J35" s="48" t="n">
+      <c r="J35" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K35" s="48" t="n">
+      <c r="K35" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L35" s="49" t="n">
+      <c r="L35" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -4116,7 +4242,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E36" s="42" t="inlineStr">
+      <c r="E36" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:25AM-2:30AM ET</t>
         </is>
@@ -4126,7 +4252,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G36" s="43" t="n">
+      <c r="G36" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H36" s="20" t="inlineStr">
@@ -4139,13 +4265,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J36" s="48" t="n">
+      <c r="J36" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K36" s="48" t="n">
+      <c r="K36" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L36" s="49" t="n">
+      <c r="L36" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -4168,7 +4294,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E37" s="46" t="inlineStr">
+      <c r="E37" s="43" t="inlineStr">
         <is>
           <t>Dogecoin Up or Down - June 24, 2:25AM-2:30AM ET</t>
         </is>
@@ -4178,7 +4304,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G37" s="47" t="n">
+      <c r="G37" s="44" t="n">
         <v>0.515</v>
       </c>
       <c r="H37" s="31" t="inlineStr">
@@ -4191,13 +4317,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J37" s="48" t="n">
+      <c r="J37" s="45" t="n">
         <v>0.9557</v>
       </c>
-      <c r="K37" s="48" t="n">
+      <c r="K37" s="45" t="n">
         <v>0.9377</v>
       </c>
-      <c r="L37" s="49" t="n">
+      <c r="L37" s="46" t="n">
         <v>1.041888888888889</v>
       </c>
     </row>
@@ -4220,7 +4346,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E38" s="42" t="inlineStr">
+      <c r="E38" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:30AM-2:35AM ET</t>
         </is>
@@ -4230,7 +4356,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G38" s="43" t="n">
+      <c r="G38" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H38" s="20" t="inlineStr">
@@ -4243,13 +4369,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J38" s="44" t="n">
+      <c r="J38" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K38" s="44" t="n">
+      <c r="K38" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L38" s="45" t="n">
+      <c r="L38" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4272,7 +4398,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E39" s="46" t="inlineStr">
+      <c r="E39" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:30AM-2:35AM ET</t>
         </is>
@@ -4282,7 +4408,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G39" s="47" t="n">
+      <c r="G39" s="44" t="n">
         <v>0.475</v>
       </c>
       <c r="H39" s="31" t="inlineStr">
@@ -4295,13 +4421,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J39" s="44" t="n">
+      <c r="J39" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K39" s="44" t="n">
+      <c r="K39" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L39" s="45" t="n">
+      <c r="L39" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4324,7 +4450,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E40" s="42" t="inlineStr">
+      <c r="E40" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:30AM-2:35AM ET</t>
         </is>
@@ -4334,7 +4460,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G40" s="43" t="n">
+      <c r="G40" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H40" s="20" t="inlineStr">
@@ -4347,13 +4473,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J40" s="48" t="n">
+      <c r="J40" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K40" s="48" t="n">
+      <c r="K40" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L40" s="49" t="n">
+      <c r="L40" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -4376,7 +4502,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E41" s="46" t="inlineStr">
+      <c r="E41" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:35AM-2:40AM ET</t>
         </is>
@@ -4386,7 +4512,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G41" s="47" t="n">
+      <c r="G41" s="44" t="n">
         <v>0.485</v>
       </c>
       <c r="H41" s="31" t="inlineStr">
@@ -4399,13 +4525,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J41" s="44" t="n">
+      <c r="J41" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K41" s="44" t="n">
+      <c r="K41" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L41" s="45" t="n">
+      <c r="L41" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4428,7 +4554,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E42" s="42" t="inlineStr">
+      <c r="E42" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:35AM-2:40AM ET</t>
         </is>
@@ -4438,7 +4564,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G42" s="43" t="n">
+      <c r="G42" s="40" t="n">
         <v>0.495</v>
       </c>
       <c r="H42" s="20" t="inlineStr">
@@ -4451,13 +4577,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J42" s="48" t="n">
+      <c r="J42" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K42" s="48" t="n">
+      <c r="K42" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L42" s="49" t="n">
+      <c r="L42" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -4480,7 +4606,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E43" s="46" t="inlineStr">
+      <c r="E43" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:35AM-2:40AM ET</t>
         </is>
@@ -4490,7 +4616,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G43" s="47" t="n">
+      <c r="G43" s="44" t="n">
         <v>0.475</v>
       </c>
       <c r="H43" s="31" t="inlineStr">
@@ -4503,13 +4629,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J43" s="48" t="n">
+      <c r="J43" s="45" t="n">
         <v>0.9947</v>
       </c>
-      <c r="K43" s="48" t="n">
+      <c r="K43" s="45" t="n">
         <v>0.9767</v>
       </c>
-      <c r="L43" s="49" t="n">
+      <c r="L43" s="46" t="n">
         <v>1.085222222222222</v>
       </c>
     </row>
@@ -4532,7 +4658,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E44" s="42" t="inlineStr">
+      <c r="E44" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:30AM-2:45AM ET</t>
         </is>
@@ -4542,7 +4668,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G44" s="43" t="n">
+      <c r="G44" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H44" s="20" t="inlineStr">
@@ -4555,13 +4681,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J44" s="44" t="n">
+      <c r="J44" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K44" s="44" t="n">
+      <c r="K44" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L44" s="45" t="n">
+      <c r="L44" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4584,7 +4710,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E45" s="46" t="inlineStr">
+      <c r="E45" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:30AM-2:45AM ET</t>
         </is>
@@ -4594,7 +4720,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G45" s="47" t="n">
+      <c r="G45" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H45" s="31" t="inlineStr">
@@ -4607,13 +4733,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J45" s="44" t="n">
+      <c r="J45" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K45" s="44" t="n">
+      <c r="K45" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L45" s="45" t="n">
+      <c r="L45" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4636,7 +4762,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E46" s="42" t="inlineStr">
+      <c r="E46" s="39" t="inlineStr">
         <is>
           <t>XRP Up or Down - June 24, 3:00AM-3:15AM ET</t>
         </is>
@@ -4646,7 +4772,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G46" s="43" t="n">
+      <c r="G46" s="40" t="n">
         <v>0.52</v>
       </c>
       <c r="H46" s="20" t="inlineStr">
@@ -4659,13 +4785,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J46" s="48" t="n">
+      <c r="J46" s="45" t="n">
         <v>0.975</v>
       </c>
-      <c r="K46" s="48" t="n">
+      <c r="K46" s="45" t="n">
         <v>0.957</v>
       </c>
-      <c r="L46" s="49" t="n">
+      <c r="L46" s="46" t="n">
         <v>1.063333333333333</v>
       </c>
     </row>
@@ -4688,7 +4814,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E47" s="46" t="inlineStr">
+      <c r="E47" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 3:00AM-3:15AM ET</t>
         </is>
@@ -4698,7 +4824,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G47" s="47" t="n">
+      <c r="G47" s="44" t="n">
         <v>0.505</v>
       </c>
       <c r="H47" s="31" t="inlineStr">
@@ -4711,13 +4837,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J47" s="48" t="n">
+      <c r="J47" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K47" s="48" t="n">
+      <c r="K47" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L47" s="49" t="n">
+      <c r="L47" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -4740,7 +4866,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E48" s="42" t="inlineStr">
+      <c r="E48" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 3:00AM-3:15AM ET</t>
         </is>
@@ -4750,7 +4876,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G48" s="43" t="n">
+      <c r="G48" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H48" s="20" t="inlineStr">
@@ -4763,13 +4889,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J48" s="48" t="n">
+      <c r="J48" s="45" t="n">
         <v>0.8822</v>
       </c>
-      <c r="K48" s="48" t="n">
+      <c r="K48" s="45" t="n">
         <v>0.8642</v>
       </c>
-      <c r="L48" s="49" t="n">
+      <c r="L48" s="46" t="n">
         <v>0.9602222222222222</v>
       </c>
     </row>
@@ -4792,7 +4918,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E49" s="46" t="inlineStr">
+      <c r="E49" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 3:15AM-3:30AM ET</t>
         </is>
@@ -4802,7 +4928,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G49" s="47" t="n">
+      <c r="G49" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H49" s="31" t="inlineStr">
@@ -4815,13 +4941,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J49" s="44" t="n">
+      <c r="J49" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K49" s="44" t="n">
+      <c r="K49" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L49" s="45" t="n">
+      <c r="L49" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4844,7 +4970,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E50" s="42" t="inlineStr">
+      <c r="E50" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 3:20AM-3:25AM ET</t>
         </is>
@@ -4854,7 +4980,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G50" s="43" t="n">
+      <c r="G50" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H50" s="20" t="inlineStr">
@@ -4867,13 +4993,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J50" s="44" t="n">
+      <c r="J50" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K50" s="44" t="n">
+      <c r="K50" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L50" s="45" t="n">
+      <c r="L50" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4896,7 +5022,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E51" s="46" t="inlineStr">
+      <c r="E51" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 3:20AM-3:25AM ET</t>
         </is>
@@ -4906,7 +5032,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G51" s="47" t="n">
+      <c r="G51" s="44" t="n">
         <v>0.505</v>
       </c>
       <c r="H51" s="31" t="inlineStr">
@@ -4919,13 +5045,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J51" s="44" t="n">
+      <c r="J51" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K51" s="44" t="n">
+      <c r="K51" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L51" s="45" t="n">
+      <c r="L51" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -4948,7 +5074,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E52" s="42" t="inlineStr">
+      <c r="E52" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 3:15AM-3:30AM ET</t>
         </is>
@@ -4958,7 +5084,7 @@
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="G52" s="43" t="n">
+      <c r="G52" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H52" s="20" t="inlineStr">
@@ -4971,13 +5097,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J52" s="48" t="n">
+      <c r="J52" s="45" t="n">
         <v>0.9182</v>
       </c>
-      <c r="K52" s="48" t="n">
+      <c r="K52" s="45" t="n">
         <v>0.9002</v>
       </c>
-      <c r="L52" s="49" t="n">
+      <c r="L52" s="46" t="n">
         <v>1.000222222222222</v>
       </c>
     </row>
@@ -5000,7 +5126,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E53" s="46" t="inlineStr">
+      <c r="E53" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 3:15AM-3:30AM ET</t>
         </is>
@@ -5010,7 +5136,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G53" s="47" t="n">
+      <c r="G53" s="44" t="n">
         <v>0.415</v>
       </c>
       <c r="H53" s="31" t="inlineStr">
@@ -5023,13 +5149,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J53" s="44" t="n">
+      <c r="J53" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K53" s="44" t="n">
+      <c r="K53" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L53" s="45" t="n">
+      <c r="L53" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5052,7 +5178,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E54" s="42" t="inlineStr">
+      <c r="E54" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 3:15AM-3:30AM ET</t>
         </is>
@@ -5062,7 +5188,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G54" s="43" t="n">
+      <c r="G54" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H54" s="20" t="inlineStr">
@@ -5075,13 +5201,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J54" s="44" t="n">
+      <c r="J54" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K54" s="44" t="n">
+      <c r="K54" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L54" s="45" t="n">
+      <c r="L54" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5104,7 +5230,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E55" s="46" t="inlineStr">
+      <c r="E55" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 3:15AM-3:30AM ET</t>
         </is>
@@ -5114,7 +5240,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G55" s="47" t="n">
+      <c r="G55" s="44" t="n">
         <v>0.435</v>
       </c>
       <c r="H55" s="31" t="inlineStr">
@@ -5127,13 +5253,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J55" s="44" t="n">
+      <c r="J55" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K55" s="44" t="n">
+      <c r="K55" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L55" s="45" t="n">
+      <c r="L55" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5156,7 +5282,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E56" s="42" t="inlineStr">
+      <c r="E56" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 3:30AM-3:45AM ET</t>
         </is>
@@ -5166,7 +5292,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G56" s="43" t="n">
+      <c r="G56" s="40" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="H56" s="20" t="inlineStr">
@@ -5179,13 +5305,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J56" s="44" t="n">
+      <c r="J56" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K56" s="44" t="n">
+      <c r="K56" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L56" s="45" t="n">
+      <c r="L56" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5208,7 +5334,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E57" s="46" t="inlineStr">
+      <c r="E57" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 3:30AM-3:45AM ET</t>
         </is>
@@ -5218,7 +5344,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G57" s="47" t="n">
+      <c r="G57" s="44" t="n">
         <v>0.635</v>
       </c>
       <c r="H57" s="31" t="inlineStr">
@@ -5231,13 +5357,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J57" s="48" t="n">
+      <c r="J57" s="45" t="n">
         <v>0.5173</v>
       </c>
-      <c r="K57" s="48" t="n">
+      <c r="K57" s="45" t="n">
         <v>0.4993</v>
       </c>
-      <c r="L57" s="49" t="n">
+      <c r="L57" s="46" t="n">
         <v>0.5547777777777778</v>
       </c>
     </row>
@@ -5260,7 +5386,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E58" s="42" t="inlineStr">
+      <c r="E58" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 3:45AM-3:50AM ET</t>
         </is>
@@ -5270,7 +5396,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G58" s="43" t="n">
+      <c r="G58" s="40" t="n">
         <v>0.505</v>
       </c>
       <c r="H58" s="20" t="inlineStr">
@@ -5283,13 +5409,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J58" s="44" t="n">
+      <c r="J58" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K58" s="44" t="n">
+      <c r="K58" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L58" s="45" t="n">
+      <c r="L58" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5312,7 +5438,7 @@
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="E59" s="46" t="inlineStr">
+      <c r="E59" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 3:45AM-3:50AM ET</t>
         </is>
@@ -5322,7 +5448,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G59" s="47" t="n">
+      <c r="G59" s="44" t="n">
         <v>0.495</v>
       </c>
       <c r="H59" s="31" t="inlineStr">
@@ -5335,13 +5461,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J59" s="44" t="n">
+      <c r="J59" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K59" s="44" t="n">
+      <c r="K59" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L59" s="45" t="n">
+      <c r="L59" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5364,7 +5490,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E60" s="42" t="inlineStr">
+      <c r="E60" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 3AM ET</t>
         </is>
@@ -5374,7 +5500,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G60" s="43" t="n">
+      <c r="G60" s="40" t="n">
         <v>0.485</v>
       </c>
       <c r="H60" s="20" t="inlineStr">
@@ -5387,13 +5513,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J60" s="44" t="n">
+      <c r="J60" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K60" s="44" t="n">
+      <c r="K60" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L60" s="45" t="n">
+      <c r="L60" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5416,7 +5542,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E61" s="46" t="inlineStr">
+      <c r="E61" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 3AM ET</t>
         </is>
@@ -5426,7 +5552,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G61" s="47" t="n">
+      <c r="G61" s="44" t="n">
         <v>0.34</v>
       </c>
       <c r="H61" s="31" t="inlineStr">
@@ -5439,13 +5565,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J61" s="44" t="n">
+      <c r="J61" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K61" s="44" t="n">
+      <c r="K61" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L61" s="45" t="n">
+      <c r="L61" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5468,7 +5594,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E62" s="42" t="inlineStr">
+      <c r="E62" s="39" t="inlineStr">
         <is>
           <t>XRP Up or Down - June 24, 3:45AM-4:00AM ET</t>
         </is>
@@ -5478,7 +5604,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G62" s="43" t="n">
+      <c r="G62" s="40" t="n">
         <v>0.525</v>
       </c>
       <c r="H62" s="20" t="inlineStr">
@@ -5491,13 +5617,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J62" s="44" t="n">
+      <c r="J62" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K62" s="44" t="n">
+      <c r="K62" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L62" s="45" t="n">
+      <c r="L62" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5520,7 +5646,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E63" s="46" t="inlineStr">
+      <c r="E63" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 12:00AM-4:00AM ET</t>
         </is>
@@ -5530,7 +5656,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G63" s="47" t="n">
+      <c r="G63" s="44" t="n">
         <v>0.615</v>
       </c>
       <c r="H63" s="31" t="inlineStr">
@@ -5543,13 +5669,13 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J63" s="44" t="n">
+      <c r="J63" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K63" s="44" t="n">
+      <c r="K63" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L63" s="45" t="n">
+      <c r="L63" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
@@ -5572,7 +5698,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E64" s="42" t="inlineStr">
+      <c r="E64" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 3:45AM-4:00AM ET</t>
         </is>
@@ -5582,7 +5708,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G64" s="43" t="n">
+      <c r="G64" s="40" t="n">
         <v>0.315</v>
       </c>
       <c r="H64" s="20" t="inlineStr">
@@ -5595,13 +5721,13 @@
           <t>✅ ACIERTO</t>
         </is>
       </c>
-      <c r="J64" s="48" t="n">
+      <c r="J64" s="45" t="n">
         <v>1.9571</v>
       </c>
-      <c r="K64" s="48" t="n">
+      <c r="K64" s="45" t="n">
         <v>1.9391</v>
       </c>
-      <c r="L64" s="49" t="n">
+      <c r="L64" s="46" t="n">
         <v>2.154555555555556</v>
       </c>
     </row>
@@ -5624,7 +5750,7 @@
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="E65" s="46" t="inlineStr">
+      <c r="E65" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 3AM ET</t>
         </is>
@@ -5634,7 +5760,7 @@
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="G65" s="47" t="n">
+      <c r="G65" s="44" t="n">
         <v>0.535</v>
       </c>
       <c r="H65" s="31" t="inlineStr">
@@ -5647,42 +5773,978 @@
           <t>❌ FALLO</t>
         </is>
       </c>
-      <c r="J65" s="44" t="n">
+      <c r="J65" s="41" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K65" s="44" t="n">
+      <c r="K65" s="41" t="n">
         <v>-0.918</v>
       </c>
-      <c r="L65" s="45" t="n">
+      <c r="L65" s="42" t="n">
         <v>-1.02</v>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 08:21</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 08:13</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E66" s="39" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 4:15AM-4:20AM ET</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G66" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H66" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>✅ ACIERTO</t>
+        </is>
+      </c>
+      <c r="J66" s="45" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="K66" s="45" t="n">
+        <v>0.9002</v>
+      </c>
+      <c r="L66" s="46" t="n">
+        <v>1.000222222222222</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="31" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 08:21</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 08:13</t>
+        </is>
+      </c>
+      <c r="D67" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E67" s="43" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 4:15AM-4:20AM ET</t>
+        </is>
+      </c>
+      <c r="F67" s="31" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G67" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H67" s="31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J67" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K67" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L67" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:03</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 08:00</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E68" s="39" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 4AM ET</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G68" s="40" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>✅ ACIERTO</t>
+        </is>
+      </c>
+      <c r="J68" s="45" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="K68" s="45" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="L68" s="46" t="n">
+        <v>1.063333333333333</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:07</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 08:58</t>
+        </is>
+      </c>
+      <c r="D69" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E69" s="43" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 5:00AM-5:05AM ET</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G69" s="44" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H69" s="31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J69" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K69" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L69" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:12</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:05</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E70" s="39" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 5:05AM-5:10AM ET</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G70" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J70" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K70" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L70" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:16</t>
+        </is>
+      </c>
+      <c r="C71" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:08</t>
+        </is>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E71" s="43" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 5:10AM-5:15AM ET</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G71" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H71" s="31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J71" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K71" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L71" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="20" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:31</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:08</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E72" s="39" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 5:15AM-5:30AM ET</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G72" s="40" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>✅ ACIERTO</t>
+        </is>
+      </c>
+      <c r="J72" s="45" t="n">
+        <v>0.8822</v>
+      </c>
+      <c r="K72" s="45" t="n">
+        <v>0.8642</v>
+      </c>
+      <c r="L72" s="46" t="n">
+        <v>0.9602222222222222</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="31" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:31</t>
+        </is>
+      </c>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:08</t>
+        </is>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E73" s="43" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 5:15AM-5:30AM ET</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G73" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H73" s="31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>✅ ACIERTO</t>
+        </is>
+      </c>
+      <c r="J73" s="45" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="K73" s="45" t="n">
+        <v>0.9002</v>
+      </c>
+      <c r="L73" s="46" t="n">
+        <v>1.000222222222222</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:46</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:38</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E74" s="39" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 5:40AM-5:45AM ET</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G74" s="40" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J74" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K74" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L74" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="31" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:46</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:38</t>
+        </is>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E75" s="43" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 5:40AM-5:45AM ET</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G75" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H75" s="31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J75" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K75" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L75" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:01</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:38</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E76" s="39" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 5:45AM-6:00AM ET</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G76" s="40" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H76" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>✅ ACIERTO</t>
+        </is>
+      </c>
+      <c r="J76" s="45" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="K76" s="45" t="n">
+        <v>0.8296</v>
+      </c>
+      <c r="L76" s="46" t="n">
+        <v>0.9217777777777778</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="31" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:01</t>
+        </is>
+      </c>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:38</t>
+        </is>
+      </c>
+      <c r="D77" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E77" s="43" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 5:45AM-6:00AM ET</t>
+        </is>
+      </c>
+      <c r="F77" s="31" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G77" s="44" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H77" s="31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>✅ ACIERTO</t>
+        </is>
+      </c>
+      <c r="J77" s="45" t="n">
+        <v>0.8143</v>
+      </c>
+      <c r="K77" s="45" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="L77" s="46" t="n">
+        <v>0.8847777777777778</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="20" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:01</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:53</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E78" s="39" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 5:55AM-6:00AM ET</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G78" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J78" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K78" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L78" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="31" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:02</t>
+        </is>
+      </c>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:53</t>
+        </is>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E79" s="43" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 5:55AM-6:00AM ET</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G79" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H79" s="31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J79" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K79" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L79" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="20" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:02</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:53</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E80" s="39" t="inlineStr">
+        <is>
+          <t>XRP Up or Down - June 24, 5:55AM-6:00AM ET</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G80" s="40" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J80" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K80" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L80" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="31" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:16</t>
+        </is>
+      </c>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:53</t>
+        </is>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E81" s="43" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 6:00AM-6:15AM ET</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G81" s="44" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H81" s="31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J81" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K81" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L81" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="20" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:21</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:13</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E82" s="39" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 6:15AM-6:20AM ET</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G82" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J82" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K82" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L82" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="31" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:27</t>
+        </is>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:21</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E83" s="43" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 6:20AM-6:25AM ET</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G83" s="44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H83" s="31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J83" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K83" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L83" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr"/>
-      <c r="C66" s="10" t="inlineStr"/>
-      <c r="D66" s="10" t="inlineStr"/>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>64 ops</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr"/>
-      <c r="G66" s="10" t="inlineStr"/>
-      <c r="H66" s="10" t="inlineStr"/>
-      <c r="I66" s="10" t="inlineStr"/>
-      <c r="J66" s="44" t="n">
-        <v>-5.7087</v>
-      </c>
-      <c r="K66" s="44" t="n">
-        <v>-6.860700000000001</v>
-      </c>
-      <c r="L66" s="45" t="n">
-        <v>-0.119109375</v>
+      <c r="B84" s="10" t="inlineStr"/>
+      <c r="C84" s="10" t="inlineStr"/>
+      <c r="D84" s="10" t="inlineStr"/>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>82 ops</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr"/>
+      <c r="G84" s="10" t="inlineStr"/>
+      <c r="H84" s="10" t="inlineStr"/>
+      <c r="I84" s="10" t="inlineStr"/>
+      <c r="J84" s="41" t="n">
+        <v>-11.15320000000001</v>
+      </c>
+      <c r="K84" s="41" t="n">
+        <v>-12.6292</v>
+      </c>
+      <c r="L84" s="42" t="n">
+        <v>-0.1711273712737127</v>
       </c>
     </row>
   </sheetData>
@@ -5764,28 +6826,28 @@
         </is>
       </c>
       <c r="B2" s="20" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C2" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="D2" s="21" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="E2" s="50" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="F2" s="50" t="n">
-        <v>-0.0252</v>
-      </c>
-      <c r="G2" s="34" t="n">
-        <v>-0.1191</v>
-      </c>
-      <c r="H2" s="34" t="n">
-        <v>-0.0023</v>
+        <v>33</v>
+      </c>
+      <c r="D2" s="32" t="n">
+        <v>0.4714</v>
+      </c>
+      <c r="E2" s="33" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="F2" s="33" t="n">
+        <v>-0.0639</v>
+      </c>
+      <c r="G2" s="23" t="n">
+        <v>-5.8876</v>
+      </c>
+      <c r="H2" s="23" t="n">
+        <v>-0.08409999999999999</v>
       </c>
       <c r="I2" s="26" t="n">
-        <v>0.1785</v>
+        <v>0.1597</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -5809,13 +6871,13 @@
       <c r="F3" s="33" t="n">
         <v>-0.0608</v>
       </c>
-      <c r="G3" s="34" t="n">
+      <c r="G3" s="23" t="n">
         <v>-6.7416</v>
       </c>
-      <c r="H3" s="34" t="n">
+      <c r="H3" s="23" t="n">
         <v>-0.5618</v>
       </c>
-      <c r="I3" s="37" t="n">
+      <c r="I3" s="34" t="n">
         <v>0.07829999999999999</v>
       </c>
     </row>
@@ -5830,7 +6892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5897,25 +6959,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B2" s="42" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $62,000 and $64,000 on June 24?</t>
         </is>
       </c>
-      <c r="D2" s="51" t="inlineStr">
+      <c r="D2" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E2" s="43" t="n">
+      <c r="E2" s="40" t="n">
         <v>0.645</v>
       </c>
-      <c r="F2" s="43" t="n">
+      <c r="F2" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G2" s="20" t="inlineStr">
@@ -5940,25 +7002,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B3" s="46" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C3" s="46" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $60,000 and $62,000 on June 24?</t>
         </is>
       </c>
-      <c r="D3" s="52" t="inlineStr">
+      <c r="D3" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E3" s="47" t="n">
+      <c r="E3" s="44" t="n">
         <v>0.202</v>
       </c>
-      <c r="F3" s="47" t="n">
+      <c r="F3" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G3" s="31" t="inlineStr">
@@ -5983,25 +7045,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $64,000 and $66,000 on June 25?</t>
         </is>
       </c>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E4" s="43" t="n">
+      <c r="E4" s="40" t="n">
         <v>0.18</v>
       </c>
-      <c r="F4" s="43" t="n">
+      <c r="F4" s="40" t="n">
         <v>-0.06</v>
       </c>
       <c r="G4" s="20" t="inlineStr">
@@ -6026,25 +7088,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B5" s="46" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C5" s="46" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $62,000 and $64,000 on June 25?</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="44" t="n">
         <v>0.475</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="F5" s="44" t="n">
         <v>0.13</v>
       </c>
       <c r="G5" s="31" t="inlineStr">
@@ -6069,25 +7131,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $60,000 and $62,000 on June 25?</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E6" s="43" t="n">
+      <c r="E6" s="40" t="n">
         <v>0.2655</v>
       </c>
-      <c r="F6" s="43" t="n">
+      <c r="F6" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -6112,25 +7174,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $62,000 and $64,000 on June 27?</t>
         </is>
       </c>
-      <c r="D7" s="51" t="inlineStr">
+      <c r="D7" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="44" t="n">
         <v>0.315</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="44" t="n">
         <v>0.13</v>
       </c>
       <c r="G7" s="31" t="inlineStr">
@@ -6155,25 +7217,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $60,000 and $62,000 on June 27?</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E8" s="43" t="n">
+      <c r="E8" s="40" t="n">
         <v>0.25</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -6198,25 +7260,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $64,000 and $66,000 on June 27?</t>
         </is>
       </c>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="44" t="n">
         <v>0.21</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G9" s="31" t="inlineStr">
@@ -6241,25 +7303,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $60,000 and $62,000 on June 28?</t>
         </is>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E10" s="40" t="n">
         <v>0.24</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -6284,25 +7346,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $62,000 and $64,000 on June 28?</t>
         </is>
       </c>
-      <c r="D11" s="51" t="inlineStr">
+      <c r="D11" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="44" t="n">
         <v>0.285</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="44" t="n">
         <v>0.13</v>
       </c>
       <c r="G11" s="31" t="inlineStr">
@@ -6327,25 +7389,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C12" s="42" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $64,000 and $66,000 on June 28?</t>
         </is>
       </c>
-      <c r="D12" s="52" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n">
+      <c r="E12" s="40" t="n">
         <v>0.21</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -6370,25 +7432,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $60,000 and $62,000 on June 29?</t>
         </is>
       </c>
-      <c r="D13" s="52" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="44" t="n">
         <v>0.23</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G13" s="31" t="inlineStr">
@@ -6413,25 +7475,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C14" s="42" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $62,000 and $64,000 on June 29?</t>
         </is>
       </c>
-      <c r="D14" s="51" t="inlineStr">
+      <c r="D14" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E14" s="43" t="n">
+      <c r="E14" s="40" t="n">
         <v>0.26</v>
       </c>
-      <c r="F14" s="43" t="n">
+      <c r="F14" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -6456,25 +7518,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be between $64,000 and $66,000 on June 29?</t>
         </is>
       </c>
-      <c r="D15" s="52" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="44" t="n">
         <v>0.195</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="44" t="n">
         <v>-0.075</v>
       </c>
       <c r="G15" s="31" t="inlineStr">
@@ -6499,25 +7561,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C16" s="42" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,600 and $1,700 on June 24?</t>
         </is>
       </c>
-      <c r="D16" s="51" t="inlineStr">
+      <c r="D16" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E16" s="43" t="n">
+      <c r="E16" s="40" t="n">
         <v>0.82</v>
       </c>
-      <c r="F16" s="43" t="n">
+      <c r="F16" s="40" t="n">
         <v>0.04</v>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -6542,25 +7604,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,700 and $1,800 on June 24?</t>
         </is>
       </c>
-      <c r="D17" s="52" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="44" t="n">
         <v>0.155</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="44" t="n">
         <v>-0.035</v>
       </c>
       <c r="G17" s="31" t="inlineStr">
@@ -6585,25 +7647,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C18" s="42" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,600 and $1,700 on June 25?</t>
         </is>
       </c>
-      <c r="D18" s="51" t="inlineStr">
+      <c r="D18" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E18" s="43" t="n">
+      <c r="E18" s="40" t="n">
         <v>0.62</v>
       </c>
-      <c r="F18" s="43" t="n">
+      <c r="F18" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -6628,25 +7690,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,700 and $1,800 on June 25?</t>
         </is>
       </c>
-      <c r="D19" s="52" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="44" t="n">
         <v>0.265</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G19" s="31" t="inlineStr">
@@ -6671,25 +7733,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C20" s="42" t="inlineStr">
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,500 and $1,600 on June 26?</t>
         </is>
       </c>
-      <c r="D20" s="52" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E20" s="43" t="n">
+      <c r="E20" s="40" t="n">
         <v>0.1545</v>
       </c>
-      <c r="F20" s="43" t="n">
+      <c r="F20" s="40" t="n">
         <v>-0.0345</v>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -6714,25 +7776,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,600 and $1,700 on June 26?</t>
         </is>
       </c>
-      <c r="D21" s="51" t="inlineStr">
+      <c r="D21" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="44" t="n">
         <v>0.52</v>
       </c>
-      <c r="F21" s="47" t="n">
+      <c r="F21" s="44" t="n">
         <v>0.13</v>
       </c>
       <c r="G21" s="31" t="inlineStr">
@@ -6757,25 +7819,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,700 and $1,800 on June 26?</t>
         </is>
       </c>
-      <c r="D22" s="52" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E22" s="43" t="n">
+      <c r="E22" s="40" t="n">
         <v>0.28</v>
       </c>
-      <c r="F22" s="43" t="n">
+      <c r="F22" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -6800,25 +7862,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,500 and $1,600 on June 27?</t>
         </is>
       </c>
-      <c r="D23" s="52" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="44" t="n">
         <v>0.175</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="44" t="n">
         <v>-0.055</v>
       </c>
       <c r="G23" s="31" t="inlineStr">
@@ -6843,25 +7905,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C24" s="42" t="inlineStr">
+      <c r="C24" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,600 and $1,700 on June 27?</t>
         </is>
       </c>
-      <c r="D24" s="51" t="inlineStr">
+      <c r="D24" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E24" s="43" t="n">
+      <c r="E24" s="40" t="n">
         <v>0.47</v>
       </c>
-      <c r="F24" s="43" t="n">
+      <c r="F24" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -6886,25 +7948,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,700 and $1,800 on June 27?</t>
         </is>
       </c>
-      <c r="D25" s="52" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="44" t="n">
         <v>0.28</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G25" s="31" t="inlineStr">
@@ -6929,25 +7991,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B26" s="42" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C26" s="42" t="inlineStr">
+      <c r="C26" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,500 and $1,600 on June 28?</t>
         </is>
       </c>
-      <c r="D26" s="52" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E26" s="43" t="n">
+      <c r="E26" s="40" t="n">
         <v>0.1895</v>
       </c>
-      <c r="F26" s="43" t="n">
+      <c r="F26" s="40" t="n">
         <v>-0.06950000000000001</v>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -6972,25 +8034,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B27" s="46" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C27" s="46" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,700 and $1,800 on June 28?</t>
         </is>
       </c>
-      <c r="D27" s="52" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="44" t="n">
         <v>0.275</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G27" s="31" t="inlineStr">
@@ -7015,25 +8077,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C28" s="42" t="inlineStr">
+      <c r="C28" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,600 and $1,700 on June 28?</t>
         </is>
       </c>
-      <c r="D28" s="51" t="inlineStr">
+      <c r="D28" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E28" s="43" t="n">
+      <c r="E28" s="40" t="n">
         <v>0.425</v>
       </c>
-      <c r="F28" s="43" t="n">
+      <c r="F28" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -7058,25 +8120,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,600 and $1,700 on June 29?</t>
         </is>
       </c>
-      <c r="D29" s="51" t="inlineStr">
+      <c r="D29" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E29" s="47" t="n">
+      <c r="E29" s="44" t="n">
         <v>0.375</v>
       </c>
-      <c r="F29" s="47" t="n">
+      <c r="F29" s="44" t="n">
         <v>0.13</v>
       </c>
       <c r="G29" s="31" t="inlineStr">
@@ -7101,25 +8163,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B30" s="42" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C30" s="42" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,500 and $1,600 on June 29?</t>
         </is>
       </c>
-      <c r="D30" s="52" t="inlineStr">
+      <c r="D30" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E30" s="43" t="n">
+      <c r="E30" s="40" t="n">
         <v>0.195</v>
       </c>
-      <c r="F30" s="43" t="n">
+      <c r="F30" s="40" t="n">
         <v>-0.075</v>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -7144,25 +8206,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B31" s="46" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C31" s="46" t="inlineStr">
+      <c r="C31" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be between $1,700 and $1,800 on June 29?</t>
         </is>
       </c>
-      <c r="D31" s="52" t="inlineStr">
+      <c r="D31" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E31" s="47" t="n">
+      <c r="E31" s="44" t="n">
         <v>0.255</v>
       </c>
-      <c r="F31" s="47" t="n">
+      <c r="F31" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G31" s="31" t="inlineStr">
@@ -7187,25 +8249,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B32" s="42" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C32" s="42" t="inlineStr">
+      <c r="C32" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $60 and $70 on June 24?</t>
         </is>
       </c>
-      <c r="D32" s="51" t="inlineStr">
+      <c r="D32" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E32" s="43" t="n">
+      <c r="E32" s="40" t="n">
         <v>0.5605</v>
       </c>
-      <c r="F32" s="43" t="n">
+      <c r="F32" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -7230,25 +8292,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C33" s="46" t="inlineStr">
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $70 and $80 on June 24?</t>
         </is>
       </c>
-      <c r="D33" s="52" t="inlineStr">
+      <c r="D33" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E33" s="47" t="n">
+      <c r="E33" s="44" t="n">
         <v>0.435</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F33" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G33" s="31" t="inlineStr">
@@ -7273,25 +8335,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C34" s="42" t="inlineStr">
+      <c r="C34" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $60 and $70 on June 25?</t>
         </is>
       </c>
-      <c r="D34" s="51" t="inlineStr">
+      <c r="D34" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E34" s="43" t="n">
+      <c r="E34" s="40" t="n">
         <v>0.55</v>
       </c>
-      <c r="F34" s="43" t="n">
+      <c r="F34" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -7316,25 +8378,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B35" s="46" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C35" s="46" t="inlineStr">
+      <c r="C35" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $70 and $80 on June 25?</t>
         </is>
       </c>
-      <c r="D35" s="52" t="inlineStr">
+      <c r="D35" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E35" s="47" t="n">
+      <c r="E35" s="44" t="n">
         <v>0.45</v>
       </c>
-      <c r="F35" s="47" t="n">
+      <c r="F35" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G35" s="31" t="inlineStr">
@@ -7359,25 +8421,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C36" s="42" t="inlineStr">
+      <c r="C36" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $60 and $70 on June 26?</t>
         </is>
       </c>
-      <c r="D36" s="51" t="inlineStr">
+      <c r="D36" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E36" s="43" t="n">
+      <c r="E36" s="40" t="n">
         <v>0.54</v>
       </c>
-      <c r="F36" s="43" t="n">
+      <c r="F36" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -7402,25 +8464,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C37" s="46" t="inlineStr">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $70 and $80 on June 26?</t>
         </is>
       </c>
-      <c r="D37" s="52" t="inlineStr">
+      <c r="D37" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E37" s="47" t="n">
+      <c r="E37" s="44" t="n">
         <v>0.445</v>
       </c>
-      <c r="F37" s="47" t="n">
+      <c r="F37" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G37" s="31" t="inlineStr">
@@ -7445,25 +8507,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B38" s="42" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C38" s="42" t="inlineStr">
+      <c r="C38" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $80 and $90 on June 26?</t>
         </is>
       </c>
-      <c r="D38" s="52" t="inlineStr">
+      <c r="D38" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E38" s="43" t="n">
+      <c r="E38" s="40" t="n">
         <v>0.4535</v>
       </c>
-      <c r="F38" s="43" t="n">
+      <c r="F38" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -7488,25 +8550,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B39" s="46" t="inlineStr">
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C39" s="46" t="inlineStr">
+      <c r="C39" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $60 and $70 on June 27?</t>
         </is>
       </c>
-      <c r="D39" s="51" t="inlineStr">
+      <c r="D39" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E39" s="47" t="n">
+      <c r="E39" s="44" t="n">
         <v>0.535</v>
       </c>
-      <c r="F39" s="47" t="n">
+      <c r="F39" s="44" t="n">
         <v>0.13</v>
       </c>
       <c r="G39" s="31" t="inlineStr">
@@ -7531,25 +8593,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B40" s="42" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C40" s="42" t="inlineStr">
+      <c r="C40" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $70 and $80 on June 27?</t>
         </is>
       </c>
-      <c r="D40" s="52" t="inlineStr">
+      <c r="D40" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E40" s="43" t="n">
+      <c r="E40" s="40" t="n">
         <v>0.45</v>
       </c>
-      <c r="F40" s="43" t="n">
+      <c r="F40" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G40" s="20" t="inlineStr">
@@ -7574,25 +8636,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B41" s="46" t="inlineStr">
+      <c r="B41" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C41" s="46" t="inlineStr">
+      <c r="C41" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $60 and $70 on June 28?</t>
         </is>
       </c>
-      <c r="D41" s="51" t="inlineStr">
+      <c r="D41" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E41" s="47" t="n">
+      <c r="E41" s="44" t="n">
         <v>0.53</v>
       </c>
-      <c r="F41" s="47" t="n">
+      <c r="F41" s="44" t="n">
         <v>0.13</v>
       </c>
       <c r="G41" s="31" t="inlineStr">
@@ -7617,25 +8679,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B42" s="42" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C42" s="42" t="inlineStr">
+      <c r="C42" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $70 and $80 on June 28?</t>
         </is>
       </c>
-      <c r="D42" s="52" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E42" s="43" t="n">
+      <c r="E42" s="40" t="n">
         <v>0.425</v>
       </c>
-      <c r="F42" s="43" t="n">
+      <c r="F42" s="40" t="n">
         <v>-0.08</v>
       </c>
       <c r="G42" s="20" t="inlineStr">
@@ -7660,25 +8722,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B43" s="46" t="inlineStr">
+      <c r="B43" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C43" s="46" t="inlineStr">
+      <c r="C43" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $70 and $80 on June 29?</t>
         </is>
       </c>
-      <c r="D43" s="52" t="inlineStr">
+      <c r="D43" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E43" s="47" t="n">
+      <c r="E43" s="44" t="n">
         <v>0.425</v>
       </c>
-      <c r="F43" s="47" t="n">
+      <c r="F43" s="44" t="n">
         <v>-0.08</v>
       </c>
       <c r="G43" s="31" t="inlineStr">
@@ -7703,25 +8765,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B44" s="42" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C44" s="42" t="inlineStr">
+      <c r="C44" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $60 and $70 on June 29?</t>
         </is>
       </c>
-      <c r="D44" s="51" t="inlineStr">
+      <c r="D44" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E44" s="43" t="n">
+      <c r="E44" s="40" t="n">
         <v>0.515</v>
       </c>
-      <c r="F44" s="43" t="n">
+      <c r="F44" s="40" t="n">
         <v>0.13</v>
       </c>
       <c r="G44" s="20" t="inlineStr">
@@ -7746,25 +8808,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B45" s="46" t="inlineStr">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C45" s="46" t="inlineStr">
+      <c r="C45" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down on June 24?</t>
         </is>
       </c>
-      <c r="D45" s="52" t="inlineStr">
+      <c r="D45" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E45" s="47" t="n">
+      <c r="E45" s="44" t="n">
         <v>0.675</v>
       </c>
-      <c r="F45" s="47" t="n">
+      <c r="F45" s="44" t="n">
         <v>-0.0545</v>
       </c>
       <c r="G45" s="31" t="inlineStr">
@@ -7789,25 +8851,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B46" s="42" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C46" s="42" t="inlineStr">
+      <c r="C46" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down on June 24?</t>
         </is>
       </c>
-      <c r="D46" s="52" t="inlineStr">
+      <c r="D46" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E46" s="43" t="n">
+      <c r="E46" s="40" t="n">
         <v>0.675</v>
       </c>
-      <c r="F46" s="43" t="n">
+      <c r="F46" s="40" t="n">
         <v>-0.0517</v>
       </c>
       <c r="G46" s="20" t="inlineStr">
@@ -7832,25 +8894,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B47" s="46" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C47" s="46" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down on June 24?</t>
         </is>
       </c>
-      <c r="D47" s="52" t="inlineStr">
+      <c r="D47" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E47" s="44" t="n">
         <v>0.75</v>
       </c>
-      <c r="F47" s="47" t="n">
+      <c r="F47" s="44" t="n">
         <v>-0.1274</v>
       </c>
       <c r="G47" s="31" t="inlineStr">
@@ -7875,25 +8937,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B48" s="42" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C48" s="42" t="inlineStr">
+      <c r="C48" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1:30AM-1:35AM ET</t>
         </is>
       </c>
-      <c r="D48" s="51" t="inlineStr">
+      <c r="D48" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E48" s="43" t="n">
+      <c r="E48" s="40" t="n">
         <v>0.485</v>
       </c>
-      <c r="F48" s="43" t="n">
+      <c r="F48" s="40" t="n">
         <v>0.0746</v>
       </c>
       <c r="G48" s="20" t="inlineStr">
@@ -7918,25 +8980,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B49" s="46" t="inlineStr">
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C49" s="46" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 1:45AM-2:00AM ET</t>
         </is>
       </c>
-      <c r="D49" s="51" t="inlineStr">
+      <c r="D49" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E49" s="47" t="n">
+      <c r="E49" s="44" t="n">
         <v>0.485</v>
       </c>
-      <c r="F49" s="47" t="n">
+      <c r="F49" s="44" t="n">
         <v>0.1008</v>
       </c>
       <c r="G49" s="31" t="inlineStr">
@@ -7961,25 +9023,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B50" s="42" t="inlineStr">
+      <c r="B50" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C50" s="42" t="inlineStr">
+      <c r="C50" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1:40AM-1:45AM ET</t>
         </is>
       </c>
-      <c r="D50" s="51" t="inlineStr">
+      <c r="D50" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E50" s="43" t="n">
+      <c r="E50" s="40" t="n">
         <v>0.495</v>
       </c>
-      <c r="F50" s="43" t="n">
+      <c r="F50" s="40" t="n">
         <v>0.3059</v>
       </c>
       <c r="G50" s="20" t="inlineStr">
@@ -8004,25 +9066,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B51" s="46" t="inlineStr">
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C51" s="46" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 1:45AM-2:00AM ET</t>
         </is>
       </c>
-      <c r="D51" s="51" t="inlineStr">
+      <c r="D51" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E51" s="47" t="n">
+      <c r="E51" s="44" t="n">
         <v>0.505</v>
       </c>
-      <c r="F51" s="47" t="n">
+      <c r="F51" s="44" t="n">
         <v>0.1773</v>
       </c>
       <c r="G51" s="31" t="inlineStr">
@@ -8047,25 +9109,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B52" s="42" t="inlineStr">
+      <c r="B52" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C52" s="42" t="inlineStr">
+      <c r="C52" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 1:50AM-1:55AM ET</t>
         </is>
       </c>
-      <c r="D52" s="52" t="inlineStr">
+      <c r="D52" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E52" s="43" t="n">
+      <c r="E52" s="40" t="n">
         <v>0.485</v>
       </c>
-      <c r="F52" s="43" t="n">
+      <c r="F52" s="40" t="n">
         <v>-0.0589</v>
       </c>
       <c r="G52" s="20" t="inlineStr">
@@ -8090,25 +9152,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B53" s="46" t="inlineStr">
+      <c r="B53" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C53" s="46" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 1:50AM-1:55AM ET</t>
         </is>
       </c>
-      <c r="D53" s="51" t="inlineStr">
+      <c r="D53" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E53" s="47" t="n">
+      <c r="E53" s="44" t="n">
         <v>0.495</v>
       </c>
-      <c r="F53" s="47" t="n">
+      <c r="F53" s="44" t="n">
         <v>0.0559</v>
       </c>
       <c r="G53" s="31" t="inlineStr">
@@ -8133,25 +9195,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B54" s="42" t="inlineStr">
+      <c r="B54" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C54" s="42" t="inlineStr">
+      <c r="C54" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:00AM-2:15AM ET</t>
         </is>
       </c>
-      <c r="D54" s="52" t="inlineStr">
+      <c r="D54" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E54" s="43" t="n">
+      <c r="E54" s="40" t="n">
         <v>0.505</v>
       </c>
-      <c r="F54" s="43" t="n">
+      <c r="F54" s="40" t="n">
         <v>-0.1833</v>
       </c>
       <c r="G54" s="20" t="inlineStr">
@@ -8176,25 +9238,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B55" s="46" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C55" s="46" t="inlineStr">
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>Dogecoin Up or Down - June 24, 1:55AM-2:00AM ET</t>
         </is>
       </c>
-      <c r="D55" s="52" t="inlineStr">
+      <c r="D55" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E55" s="47" t="n">
+      <c r="E55" s="44" t="n">
         <v>0.515</v>
       </c>
-      <c r="F55" s="47" t="n">
+      <c r="F55" s="44" t="n">
         <v>-0.4094</v>
       </c>
       <c r="G55" s="31" t="inlineStr">
@@ -8219,25 +9281,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B56" s="42" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C56" s="42" t="inlineStr">
+      <c r="C56" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 4:00AM-8:00AM ET</t>
         </is>
       </c>
-      <c r="D56" s="52" t="inlineStr">
+      <c r="D56" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E56" s="43" t="n">
+      <c r="E56" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F56" s="43" t="n">
+      <c r="F56" s="40" t="n">
         <v>-0.0497</v>
       </c>
       <c r="G56" s="20" t="inlineStr">
@@ -8262,25 +9324,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B57" s="46" t="inlineStr">
+      <c r="B57" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C57" s="46" t="inlineStr">
+      <c r="C57" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 4:00AM-8:00AM ET</t>
         </is>
       </c>
-      <c r="D57" s="52" t="inlineStr">
+      <c r="D57" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E57" s="47" t="n">
+      <c r="E57" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F57" s="47" t="n">
+      <c r="F57" s="44" t="n">
         <v>-0.0476</v>
       </c>
       <c r="G57" s="31" t="inlineStr">
@@ -8305,25 +9367,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B58" s="42" t="inlineStr">
+      <c r="B58" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C58" s="42" t="inlineStr">
+      <c r="C58" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:00AM-2:05AM ET</t>
         </is>
       </c>
-      <c r="D58" s="52" t="inlineStr">
+      <c r="D58" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E58" s="43" t="n">
+      <c r="E58" s="40" t="n">
         <v>0.23</v>
       </c>
-      <c r="F58" s="43" t="n">
+      <c r="F58" s="40" t="n">
         <v>-0.138</v>
       </c>
       <c r="G58" s="20" t="inlineStr">
@@ -8348,25 +9410,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B59" s="46" t="inlineStr">
+      <c r="B59" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C59" s="46" t="inlineStr">
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 2:00AM-2:05AM ET</t>
         </is>
       </c>
-      <c r="D59" s="52" t="inlineStr">
+      <c r="D59" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E59" s="47" t="n">
+      <c r="E59" s="44" t="n">
         <v>0.245</v>
       </c>
-      <c r="F59" s="47" t="n">
+      <c r="F59" s="44" t="n">
         <v>-0.175</v>
       </c>
       <c r="G59" s="31" t="inlineStr">
@@ -8391,25 +9453,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B60" s="42" t="inlineStr">
+      <c r="B60" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C60" s="42" t="inlineStr">
+      <c r="C60" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:15AM-2:30AM ET</t>
         </is>
       </c>
-      <c r="D60" s="51" t="inlineStr">
+      <c r="D60" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E60" s="43" t="n">
+      <c r="E60" s="40" t="n">
         <v>0.505</v>
       </c>
-      <c r="F60" s="43" t="n">
+      <c r="F60" s="40" t="n">
         <v>0.2116</v>
       </c>
       <c r="G60" s="20" t="inlineStr">
@@ -8434,25 +9496,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B61" s="46" t="inlineStr">
+      <c r="B61" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C61" s="46" t="inlineStr">
+      <c r="C61" s="43" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:10AM-2:15AM ET</t>
         </is>
       </c>
-      <c r="D61" s="51" t="inlineStr">
+      <c r="D61" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E61" s="47" t="n">
+      <c r="E61" s="44" t="n">
         <v>0.495</v>
       </c>
-      <c r="F61" s="47" t="n">
+      <c r="F61" s="44" t="n">
         <v>0.3399</v>
       </c>
       <c r="G61" s="31" t="inlineStr">
@@ -8477,25 +9539,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B62" s="42" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C62" s="42" t="inlineStr">
+      <c r="C62" s="39" t="inlineStr">
         <is>
           <t>Bitcoin Up or Down - June 24, 2:30AM-2:45AM ET</t>
         </is>
       </c>
-      <c r="D62" s="51" t="inlineStr">
+      <c r="D62" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E62" s="43" t="n">
+      <c r="E62" s="40" t="n">
         <v>0.495</v>
       </c>
-      <c r="F62" s="43" t="n">
+      <c r="F62" s="40" t="n">
         <v>0.119</v>
       </c>
       <c r="G62" s="20" t="inlineStr">
@@ -8520,25 +9582,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B63" s="46" t="inlineStr">
+      <c r="B63" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C63" s="46" t="inlineStr">
+      <c r="C63" s="43" t="inlineStr">
         <is>
           <t>BNB Up or Down - June 24, 2:30AM-2:45AM ET</t>
         </is>
       </c>
-      <c r="D63" s="51" t="inlineStr">
+      <c r="D63" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E63" s="47" t="n">
+      <c r="E63" s="44" t="n">
         <v>0.475</v>
       </c>
-      <c r="F63" s="47" t="n">
+      <c r="F63" s="44" t="n">
         <v>0.09470000000000001</v>
       </c>
       <c r="G63" s="31" t="inlineStr">
@@ -8563,25 +9625,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B64" s="42" t="inlineStr">
+      <c r="B64" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C64" s="42" t="inlineStr">
+      <c r="C64" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 2:45AM-3:00AM ET</t>
         </is>
       </c>
-      <c r="D64" s="52" t="inlineStr">
+      <c r="D64" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E64" s="43" t="n">
+      <c r="E64" s="40" t="n">
         <v>0.505</v>
       </c>
-      <c r="F64" s="43" t="n">
+      <c r="F64" s="40" t="n">
         <v>-0.0493</v>
       </c>
       <c r="G64" s="20" t="inlineStr">
@@ -8606,25 +9668,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B65" s="46" t="inlineStr">
+      <c r="B65" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C65" s="46" t="inlineStr">
+      <c r="C65" s="43" t="inlineStr">
         <is>
           <t>Will Bitcoin reach $67,500 in June?</t>
         </is>
       </c>
-      <c r="D65" s="52" t="inlineStr">
+      <c r="D65" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E65" s="47" t="n">
+      <c r="E65" s="44" t="n">
         <v>0.135</v>
       </c>
-      <c r="F65" s="47" t="n">
+      <c r="F65" s="44" t="n">
         <v>-0.065</v>
       </c>
       <c r="G65" s="31" t="inlineStr">
@@ -8649,25 +9711,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B66" s="42" t="inlineStr">
+      <c r="B66" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C66" s="42" t="inlineStr">
+      <c r="C66" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $62,000 on June 24?</t>
         </is>
       </c>
-      <c r="D66" s="51" t="inlineStr">
+      <c r="D66" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E66" s="43" t="n">
+      <c r="E66" s="40" t="n">
         <v>0.8425</v>
       </c>
-      <c r="F66" s="43" t="n">
+      <c r="F66" s="40" t="n">
         <v>0.08749999999999999</v>
       </c>
       <c r="G66" s="20" t="inlineStr">
@@ -8692,25 +9754,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B67" s="46" t="inlineStr">
+      <c r="B67" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C67" s="46" t="inlineStr">
+      <c r="C67" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $64,000 on June 25?</t>
         </is>
       </c>
-      <c r="D67" s="52" t="inlineStr">
+      <c r="D67" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E67" s="47" t="n">
+      <c r="E67" s="44" t="n">
         <v>0.175</v>
       </c>
-      <c r="F67" s="47" t="n">
+      <c r="F67" s="44" t="n">
         <v>-0.105</v>
       </c>
       <c r="G67" s="31" t="inlineStr">
@@ -8735,25 +9797,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B68" s="42" t="inlineStr">
+      <c r="B68" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C68" s="42" t="inlineStr">
+      <c r="C68" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $62,000 on June 25?</t>
         </is>
       </c>
-      <c r="D68" s="51" t="inlineStr">
+      <c r="D68" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E68" s="43" t="n">
+      <c r="E68" s="40" t="n">
         <v>0.715</v>
       </c>
-      <c r="F68" s="43" t="n">
+      <c r="F68" s="40" t="n">
         <v>0.074</v>
       </c>
       <c r="G68" s="20" t="inlineStr">
@@ -8778,25 +9840,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B69" s="46" t="inlineStr">
+      <c r="B69" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C69" s="46" t="inlineStr">
+      <c r="C69" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $62,000 on June 26?</t>
         </is>
       </c>
-      <c r="D69" s="51" t="inlineStr">
+      <c r="D69" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E69" s="47" t="n">
+      <c r="E69" s="44" t="n">
         <v>0.66</v>
       </c>
-      <c r="F69" s="47" t="n">
+      <c r="F69" s="44" t="n">
         <v>0.067</v>
       </c>
       <c r="G69" s="31" t="inlineStr">
@@ -8821,25 +9883,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B70" s="42" t="inlineStr">
+      <c r="B70" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C70" s="42" t="inlineStr">
+      <c r="C70" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $64,000 on June 26?</t>
         </is>
       </c>
-      <c r="D70" s="52" t="inlineStr">
+      <c r="D70" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E70" s="43" t="n">
+      <c r="E70" s="40" t="n">
         <v>0.255</v>
       </c>
-      <c r="F70" s="43" t="n">
+      <c r="F70" s="40" t="n">
         <v>-0.134</v>
       </c>
       <c r="G70" s="20" t="inlineStr">
@@ -8864,25 +9926,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B71" s="46" t="inlineStr">
+      <c r="B71" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C71" s="46" t="inlineStr">
+      <c r="C71" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $64,000 on June 27?</t>
         </is>
       </c>
-      <c r="D71" s="52" t="inlineStr">
+      <c r="D71" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E71" s="47" t="n">
+      <c r="E71" s="44" t="n">
         <v>0.295</v>
       </c>
-      <c r="F71" s="47" t="n">
+      <c r="F71" s="44" t="n">
         <v>-0.1327</v>
       </c>
       <c r="G71" s="31" t="inlineStr">
@@ -8907,25 +9969,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B72" s="42" t="inlineStr">
+      <c r="B72" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C72" s="42" t="inlineStr">
+      <c r="C72" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $62,000 on June 27?</t>
         </is>
       </c>
-      <c r="D72" s="51" t="inlineStr">
+      <c r="D72" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E72" s="43" t="n">
+      <c r="E72" s="40" t="n">
         <v>0.66</v>
       </c>
-      <c r="F72" s="43" t="n">
+      <c r="F72" s="40" t="n">
         <v>0.0315</v>
       </c>
       <c r="G72" s="20" t="inlineStr">
@@ -8950,25 +10012,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B73" s="46" t="inlineStr">
+      <c r="B73" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C73" s="46" t="inlineStr">
+      <c r="C73" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $60,000 on June 27?</t>
         </is>
       </c>
-      <c r="D73" s="51" t="inlineStr">
+      <c r="D73" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E73" s="47" t="n">
+      <c r="E73" s="44" t="n">
         <v>0.904</v>
       </c>
-      <c r="F73" s="47" t="n">
+      <c r="F73" s="44" t="n">
         <v>0.026</v>
       </c>
       <c r="G73" s="31" t="inlineStr">
@@ -8993,25 +10055,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B74" s="42" t="inlineStr">
+      <c r="B74" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C74" s="42" t="inlineStr">
+      <c r="C74" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $60,000 on June 28?</t>
         </is>
       </c>
-      <c r="D74" s="51" t="inlineStr">
+      <c r="D74" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E74" s="43" t="n">
+      <c r="E74" s="40" t="n">
         <v>0.8655</v>
       </c>
-      <c r="F74" s="43" t="n">
+      <c r="F74" s="40" t="n">
         <v>0.0645</v>
       </c>
       <c r="G74" s="20" t="inlineStr">
@@ -9036,25 +10098,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B75" s="46" t="inlineStr">
+      <c r="B75" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C75" s="46" t="inlineStr">
+      <c r="C75" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $64,000 on June 28?</t>
         </is>
       </c>
-      <c r="D75" s="52" t="inlineStr">
+      <c r="D75" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E75" s="47" t="n">
+      <c r="E75" s="44" t="n">
         <v>0.315</v>
       </c>
-      <c r="F75" s="47" t="n">
+      <c r="F75" s="44" t="n">
         <v>-0.1214</v>
       </c>
       <c r="G75" s="31" t="inlineStr">
@@ -9079,25 +10141,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B76" s="42" t="inlineStr">
+      <c r="B76" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C76" s="42" t="inlineStr">
+      <c r="C76" s="39" t="inlineStr">
         <is>
           <t>Will Bitcoin reach $66,000 June 22-28?</t>
         </is>
       </c>
-      <c r="D76" s="52" t="inlineStr">
+      <c r="D76" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E76" s="43" t="n">
+      <c r="E76" s="40" t="n">
         <v>0.165</v>
       </c>
-      <c r="F76" s="43" t="n">
+      <c r="F76" s="40" t="n">
         <v>-0.095</v>
       </c>
       <c r="G76" s="20" t="inlineStr">
@@ -9122,25 +10184,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B77" s="46" t="inlineStr">
+      <c r="B77" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C77" s="46" t="inlineStr">
+      <c r="C77" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $60,000 on June 29?</t>
         </is>
       </c>
-      <c r="D77" s="51" t="inlineStr">
+      <c r="D77" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E77" s="47" t="n">
+      <c r="E77" s="44" t="n">
         <v>0.855</v>
       </c>
-      <c r="F77" s="47" t="n">
+      <c r="F77" s="44" t="n">
         <v>0.075</v>
       </c>
       <c r="G77" s="31" t="inlineStr">
@@ -9165,25 +10227,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B78" s="42" t="inlineStr">
+      <c r="B78" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C78" s="42" t="inlineStr">
+      <c r="C78" s="39" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $64,000 on June 29?</t>
         </is>
       </c>
-      <c r="D78" s="52" t="inlineStr">
+      <c r="D78" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E78" s="43" t="n">
+      <c r="E78" s="40" t="n">
         <v>0.335</v>
       </c>
-      <c r="F78" s="43" t="n">
+      <c r="F78" s="40" t="n">
         <v>-0.1168</v>
       </c>
       <c r="G78" s="20" t="inlineStr">
@@ -9208,25 +10270,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B79" s="46" t="inlineStr">
+      <c r="B79" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C79" s="46" t="inlineStr">
+      <c r="C79" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $66,000 on June 29?</t>
         </is>
       </c>
-      <c r="D79" s="52" t="inlineStr">
+      <c r="D79" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E79" s="47" t="n">
+      <c r="E79" s="44" t="n">
         <v>0.115</v>
       </c>
-      <c r="F79" s="47" t="n">
+      <c r="F79" s="44" t="n">
         <v>-0.045</v>
       </c>
       <c r="G79" s="31" t="inlineStr">
@@ -9251,25 +10313,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B80" s="42" t="inlineStr">
+      <c r="B80" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C80" s="42" t="inlineStr">
+      <c r="C80" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,700 on June 24?</t>
         </is>
       </c>
-      <c r="D80" s="52" t="inlineStr">
+      <c r="D80" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E80" s="43" t="n">
+      <c r="E80" s="40" t="n">
         <v>0.155</v>
       </c>
-      <c r="F80" s="43" t="n">
+      <c r="F80" s="40" t="n">
         <v>-0.08500000000000001</v>
       </c>
       <c r="G80" s="20" t="inlineStr">
@@ -9294,25 +10356,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B81" s="46" t="inlineStr">
+      <c r="B81" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C81" s="46" t="inlineStr">
+      <c r="C81" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,600 on June 25?</t>
         </is>
       </c>
-      <c r="D81" s="51" t="inlineStr">
+      <c r="D81" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E81" s="47" t="n">
+      <c r="E81" s="44" t="n">
         <v>0.9025</v>
       </c>
-      <c r="F81" s="47" t="n">
+      <c r="F81" s="44" t="n">
         <v>0.0275</v>
       </c>
       <c r="G81" s="31" t="inlineStr">
@@ -9337,25 +10399,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B82" s="42" t="inlineStr">
+      <c r="B82" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C82" s="42" t="inlineStr">
+      <c r="C82" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,700 on June 25?</t>
         </is>
       </c>
-      <c r="D82" s="52" t="inlineStr">
+      <c r="D82" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E82" s="43" t="n">
+      <c r="E82" s="40" t="n">
         <v>0.31</v>
       </c>
-      <c r="F82" s="43" t="n">
+      <c r="F82" s="40" t="n">
         <v>-0.1586</v>
       </c>
       <c r="G82" s="20" t="inlineStr">
@@ -9380,25 +10442,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B83" s="46" t="inlineStr">
+      <c r="B83" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C83" s="46" t="inlineStr">
+      <c r="C83" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,600 on June 26?</t>
         </is>
       </c>
-      <c r="D83" s="51" t="inlineStr">
+      <c r="D83" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E83" s="47" t="n">
+      <c r="E83" s="44" t="n">
         <v>0.84</v>
       </c>
-      <c r="F83" s="47" t="n">
+      <c r="F83" s="44" t="n">
         <v>0.09</v>
       </c>
       <c r="G83" s="31" t="inlineStr">
@@ -9423,25 +10485,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B84" s="42" t="inlineStr">
+      <c r="B84" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C84" s="42" t="inlineStr">
+      <c r="C84" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,700 on June 26?</t>
         </is>
       </c>
-      <c r="D84" s="52" t="inlineStr">
+      <c r="D84" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E84" s="43" t="n">
+      <c r="E84" s="40" t="n">
         <v>0.35</v>
       </c>
-      <c r="F84" s="43" t="n">
+      <c r="F84" s="40" t="n">
         <v>-0.1329</v>
       </c>
       <c r="G84" s="20" t="inlineStr">
@@ -9466,25 +10528,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B85" s="46" t="inlineStr">
+      <c r="B85" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C85" s="46" t="inlineStr">
+      <c r="C85" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,600 on June 27?</t>
         </is>
       </c>
-      <c r="D85" s="51" t="inlineStr">
+      <c r="D85" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E85" s="47" t="n">
+      <c r="E85" s="44" t="n">
         <v>0.825</v>
       </c>
-      <c r="F85" s="47" t="n">
+      <c r="F85" s="44" t="n">
         <v>0.105</v>
       </c>
       <c r="G85" s="31" t="inlineStr">
@@ -9509,25 +10571,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B86" s="42" t="inlineStr">
+      <c r="B86" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C86" s="42" t="inlineStr">
+      <c r="C86" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,700 on June 27?</t>
         </is>
       </c>
-      <c r="D86" s="52" t="inlineStr">
+      <c r="D86" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E86" s="43" t="n">
+      <c r="E86" s="40" t="n">
         <v>0.355</v>
       </c>
-      <c r="F86" s="43" t="n">
+      <c r="F86" s="40" t="n">
         <v>-0.09760000000000001</v>
       </c>
       <c r="G86" s="20" t="inlineStr">
@@ -9552,25 +10614,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B87" s="46" t="inlineStr">
+      <c r="B87" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C87" s="46" t="inlineStr">
+      <c r="C87" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,600 on June 28?</t>
         </is>
       </c>
-      <c r="D87" s="51" t="inlineStr">
+      <c r="D87" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E87" s="47" t="n">
+      <c r="E87" s="44" t="n">
         <v>0.8</v>
       </c>
-      <c r="F87" s="47" t="n">
+      <c r="F87" s="44" t="n">
         <v>0.1278</v>
       </c>
       <c r="G87" s="31" t="inlineStr">
@@ -9595,25 +10657,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B88" s="42" t="inlineStr">
+      <c r="B88" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C88" s="42" t="inlineStr">
+      <c r="C88" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,700 on June 28?</t>
         </is>
       </c>
-      <c r="D88" s="52" t="inlineStr">
+      <c r="D88" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E88" s="43" t="n">
+      <c r="E88" s="40" t="n">
         <v>0.38</v>
       </c>
-      <c r="F88" s="43" t="n">
+      <c r="F88" s="40" t="n">
         <v>-0.0949</v>
       </c>
       <c r="G88" s="20" t="inlineStr">
@@ -9638,25 +10700,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B89" s="46" t="inlineStr">
+      <c r="B89" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C89" s="46" t="inlineStr">
+      <c r="C89" s="43" t="inlineStr">
         <is>
           <t>Will Ethereum reach $1,800 June 22-28?</t>
         </is>
       </c>
-      <c r="D89" s="52" t="inlineStr">
+      <c r="D89" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E89" s="47" t="n">
+      <c r="E89" s="44" t="n">
         <v>0.16</v>
       </c>
-      <c r="F89" s="47" t="n">
+      <c r="F89" s="44" t="n">
         <v>-0.09</v>
       </c>
       <c r="G89" s="31" t="inlineStr">
@@ -9681,25 +10743,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B90" s="42" t="inlineStr">
+      <c r="B90" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C90" s="42" t="inlineStr">
+      <c r="C90" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,600 on June 29?</t>
         </is>
       </c>
-      <c r="D90" s="51" t="inlineStr">
+      <c r="D90" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E90" s="43" t="n">
+      <c r="E90" s="40" t="n">
         <v>0.77</v>
       </c>
-      <c r="F90" s="43" t="n">
+      <c r="F90" s="40" t="n">
         <v>0.1386</v>
       </c>
       <c r="G90" s="20" t="inlineStr">
@@ -9724,25 +10786,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B91" s="46" t="inlineStr">
+      <c r="B91" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C91" s="46" t="inlineStr">
+      <c r="C91" s="43" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,700 on June 29?</t>
         </is>
       </c>
-      <c r="D91" s="52" t="inlineStr">
+      <c r="D91" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E91" s="47" t="n">
+      <c r="E91" s="44" t="n">
         <v>0.39</v>
       </c>
-      <c r="F91" s="47" t="n">
+      <c r="F91" s="44" t="n">
         <v>-0.0844</v>
       </c>
       <c r="G91" s="31" t="inlineStr">
@@ -9767,25 +10829,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B92" s="42" t="inlineStr">
+      <c r="B92" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C92" s="42" t="inlineStr">
+      <c r="C92" s="39" t="inlineStr">
         <is>
           <t>Will the price of Ethereum be above $1,800 on June 29?</t>
         </is>
       </c>
-      <c r="D92" s="52" t="inlineStr">
+      <c r="D92" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E92" s="43" t="n">
+      <c r="E92" s="40" t="n">
         <v>0.105</v>
       </c>
-      <c r="F92" s="43" t="n">
+      <c r="F92" s="40" t="n">
         <v>-0.035</v>
       </c>
       <c r="G92" s="20" t="inlineStr">
@@ -9810,25 +10872,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B93" s="46" t="inlineStr">
+      <c r="B93" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C93" s="46" t="inlineStr">
+      <c r="C93" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be above $70 on June 24?</t>
         </is>
       </c>
-      <c r="D93" s="52" t="inlineStr">
+      <c r="D93" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E93" s="47" t="n">
+      <c r="E93" s="44" t="n">
         <v>0.425</v>
       </c>
-      <c r="F93" s="47" t="n">
+      <c r="F93" s="44" t="n">
         <v>-0.3071</v>
       </c>
       <c r="G93" s="31" t="inlineStr">
@@ -9853,25 +10915,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B94" s="42" t="inlineStr">
+      <c r="B94" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C94" s="42" t="inlineStr">
+      <c r="C94" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be above $70 on June 25?</t>
         </is>
       </c>
-      <c r="D94" s="52" t="inlineStr">
+      <c r="D94" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E94" s="43" t="n">
+      <c r="E94" s="40" t="n">
         <v>0.46</v>
       </c>
-      <c r="F94" s="43" t="n">
+      <c r="F94" s="40" t="n">
         <v>-0.1206</v>
       </c>
       <c r="G94" s="20" t="inlineStr">
@@ -9896,25 +10958,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B95" s="46" t="inlineStr">
+      <c r="B95" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C95" s="46" t="inlineStr">
+      <c r="C95" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be above $70 on June 26?</t>
         </is>
       </c>
-      <c r="D95" s="52" t="inlineStr">
+      <c r="D95" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E95" s="47" t="n">
+      <c r="E95" s="44" t="n">
         <v>0.455</v>
       </c>
-      <c r="F95" s="47" t="n">
+      <c r="F95" s="44" t="n">
         <v>-0.0745</v>
       </c>
       <c r="G95" s="31" t="inlineStr">
@@ -9939,25 +11001,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B96" s="42" t="inlineStr">
+      <c r="B96" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C96" s="42" t="inlineStr">
+      <c r="C96" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be above $70 on June 27?</t>
         </is>
       </c>
-      <c r="D96" s="52" t="inlineStr">
+      <c r="D96" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E96" s="43" t="n">
+      <c r="E96" s="40" t="n">
         <v>0.46</v>
       </c>
-      <c r="F96" s="43" t="n">
+      <c r="F96" s="40" t="n">
         <v>-0.0577</v>
       </c>
       <c r="G96" s="20" t="inlineStr">
@@ -9982,25 +11044,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B97" s="46" t="inlineStr">
+      <c r="B97" s="43" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C97" s="46" t="inlineStr">
+      <c r="C97" s="43" t="inlineStr">
         <is>
           <t>Will the price of Solana be above $70 on June 28?</t>
         </is>
       </c>
-      <c r="D97" s="52" t="inlineStr">
+      <c r="D97" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E97" s="47" t="n">
+      <c r="E97" s="44" t="n">
         <v>0.46</v>
       </c>
-      <c r="F97" s="47" t="n">
+      <c r="F97" s="44" t="n">
         <v>-0.0437</v>
       </c>
       <c r="G97" s="31" t="inlineStr">
@@ -10025,25 +11087,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B98" s="42" t="inlineStr">
+      <c r="B98" s="39" t="inlineStr">
         <is>
           <t>PRICE_TARGET_GBM</t>
         </is>
       </c>
-      <c r="C98" s="42" t="inlineStr">
+      <c r="C98" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be above $70 on June 29?</t>
         </is>
       </c>
-      <c r="D98" s="52" t="inlineStr">
+      <c r="D98" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E98" s="43" t="n">
+      <c r="E98" s="40" t="n">
         <v>0.475</v>
       </c>
-      <c r="F98" s="43" t="n">
+      <c r="F98" s="40" t="n">
         <v>-0.0488</v>
       </c>
       <c r="G98" s="20" t="inlineStr">
@@ -10068,25 +11130,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B99" s="46" t="inlineStr">
+      <c r="B99" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C99" s="46" t="inlineStr">
+      <c r="C99" s="43" t="inlineStr">
         <is>
           <t>XRP Up or Down - June 24, 3:15AM-3:30AM ET</t>
         </is>
       </c>
-      <c r="D99" s="52" t="inlineStr">
+      <c r="D99" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E99" s="47" t="n">
+      <c r="E99" s="44" t="n">
         <v>0.52</v>
       </c>
-      <c r="F99" s="47" t="n">
+      <c r="F99" s="44" t="n">
         <v>-0.1376</v>
       </c>
       <c r="G99" s="31" t="inlineStr">
@@ -10111,25 +11173,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B100" s="42" t="inlineStr">
+      <c r="B100" s="39" t="inlineStr">
         <is>
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="C100" s="42" t="inlineStr">
+      <c r="C100" s="39" t="inlineStr">
         <is>
           <t>XRP Up or Down - June 24, 3:15AM-3:30AM ET</t>
         </is>
       </c>
-      <c r="D100" s="51" t="inlineStr">
+      <c r="D100" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E100" s="43" t="n">
+      <c r="E100" s="40" t="n">
         <v>0.52</v>
       </c>
-      <c r="F100" s="43" t="n">
+      <c r="F100" s="40" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G100" s="20" t="inlineStr">
@@ -10154,25 +11216,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B101" s="46" t="inlineStr">
+      <c r="B101" s="43" t="inlineStr">
         <is>
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="C101" s="46" t="inlineStr">
+      <c r="C101" s="43" t="inlineStr">
         <is>
           <t>Will the price of Bitcoin be above $62,000 on June 24?</t>
         </is>
       </c>
-      <c r="D101" s="51" t="inlineStr">
+      <c r="D101" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E101" s="47" t="n">
+      <c r="E101" s="44" t="n">
         <v>0.8385</v>
       </c>
-      <c r="F101" s="47" t="n">
+      <c r="F101" s="44" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G101" s="31" t="inlineStr">
@@ -10197,25 +11259,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B102" s="42" t="inlineStr">
+      <c r="B102" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C102" s="42" t="inlineStr">
+      <c r="C102" s="39" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 3:30AM-3:45AM ET</t>
         </is>
       </c>
-      <c r="D102" s="51" t="inlineStr">
+      <c r="D102" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E102" s="43" t="n">
+      <c r="E102" s="40" t="n">
         <v>0.505</v>
       </c>
-      <c r="F102" s="43" t="n">
+      <c r="F102" s="40" t="n">
         <v>0.0223</v>
       </c>
       <c r="G102" s="20" t="inlineStr">
@@ -10240,25 +11302,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B103" s="46" t="inlineStr">
+      <c r="B103" s="43" t="inlineStr">
         <is>
           <t>SMART_FLOW_1H</t>
         </is>
       </c>
-      <c r="C103" s="46" t="inlineStr">
+      <c r="C103" s="43" t="inlineStr">
         <is>
           <t>Solana Up or Down - June 24, 3:30AM-3:45AM ET</t>
         </is>
       </c>
-      <c r="D103" s="51" t="inlineStr">
+      <c r="D103" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E103" s="47" t="n">
+      <c r="E103" s="44" t="n">
         <v>0.585</v>
       </c>
-      <c r="F103" s="47" t="n">
+      <c r="F103" s="44" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G103" s="31" t="inlineStr">
@@ -10283,25 +11345,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B104" s="42" t="inlineStr">
+      <c r="B104" s="39" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C104" s="42" t="inlineStr">
+      <c r="C104" s="39" t="inlineStr">
         <is>
           <t>Ethereum Up or Down - June 24, 3:45AM-3:50AM ET</t>
         </is>
       </c>
-      <c r="D104" s="51" t="inlineStr">
+      <c r="D104" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E104" s="43" t="n">
+      <c r="E104" s="40" t="n">
         <v>0.505</v>
       </c>
-      <c r="F104" s="43" t="n">
+      <c r="F104" s="40" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G104" s="20" t="inlineStr">
@@ -10326,25 +11388,25 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B105" s="46" t="inlineStr">
+      <c r="B105" s="43" t="inlineStr">
         <is>
           <t>UPDOWN_GBM</t>
         </is>
       </c>
-      <c r="C105" s="46" t="inlineStr">
+      <c r="C105" s="43" t="inlineStr">
         <is>
           <t>XRP Up or Down - June 24, 3:45AM-3:50AM ET</t>
         </is>
       </c>
-      <c r="D105" s="51" t="inlineStr">
+      <c r="D105" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E105" s="47" t="n">
+      <c r="E105" s="44" t="n">
         <v>0.505</v>
       </c>
-      <c r="F105" s="47" t="n">
+      <c r="F105" s="44" t="n">
         <v>0.0934</v>
       </c>
       <c r="G105" s="31" t="inlineStr">
@@ -10369,40 +11431,40 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B106" s="42" t="inlineStr">
-        <is>
-          <t>UPDOWN_GBM</t>
-        </is>
-      </c>
-      <c r="C106" s="42" t="inlineStr">
-        <is>
-          <t>Ethereum Up or Down - June 24, 4AM ET</t>
-        </is>
-      </c>
-      <c r="D106" s="51" t="inlineStr">
+      <c r="B106" s="39" t="inlineStr">
+        <is>
+          <t>SMART_FLOW_1H</t>
+        </is>
+      </c>
+      <c r="C106" s="39" t="inlineStr">
+        <is>
+          <t>Will Bitcoin dip to $57,500 in June?</t>
+        </is>
+      </c>
+      <c r="D106" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E106" s="43" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F106" s="43" t="n">
-        <v>0.0417</v>
+      <c r="E106" s="40" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="F106" s="40" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G106" s="20" t="inlineStr">
         <is>
-          <t>1.0h</t>
+          <t>163.9h</t>
         </is>
       </c>
       <c r="H106" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24 09:00</t>
+          <t>2026-07-01 04:00</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24 08:00</t>
+          <t>2026-06-24 08:05</t>
         </is>
       </c>
     </row>
@@ -10412,40 +11474,40 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B107" s="46" t="inlineStr">
-        <is>
-          <t>SMART_FLOW_1H</t>
-        </is>
-      </c>
-      <c r="C107" s="46" t="inlineStr">
-        <is>
-          <t>Will Bitcoin dip to $57,500 in June?</t>
-        </is>
-      </c>
-      <c r="D107" s="51" t="inlineStr">
+      <c r="B107" s="43" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C107" s="43" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 4:15AM-4:20AM ET</t>
+        </is>
+      </c>
+      <c r="D107" s="47" t="inlineStr">
         <is>
           <t>BUY_YES</t>
         </is>
       </c>
-      <c r="E107" s="47" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="F107" s="47" t="n">
-        <v>0.07000000000000001</v>
+      <c r="E107" s="44" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="F107" s="44" t="n">
+        <v>0.0376</v>
       </c>
       <c r="G107" s="31" t="inlineStr">
         <is>
-          <t>163.9h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H107" s="31" t="inlineStr">
         <is>
-          <t>2026-07-01 04:00</t>
+          <t>2026-06-24 08:20</t>
         </is>
       </c>
       <c r="I107" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24 08:05</t>
+          <t>2026-06-24 08:13</t>
         </is>
       </c>
     </row>
@@ -10455,40 +11517,40 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B108" s="42" t="inlineStr">
-        <is>
-          <t>WEEKLY_PRICE</t>
-        </is>
-      </c>
-      <c r="C108" s="42" t="inlineStr">
-        <is>
-          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
-        </is>
-      </c>
-      <c r="D108" s="52" t="inlineStr">
+      <c r="B108" s="39" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C108" s="39" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 4:40AM-4:45AM ET</t>
+        </is>
+      </c>
+      <c r="D108" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E108" s="43" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="F108" s="43" t="n">
-        <v>-0.024</v>
+      <c r="E108" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F108" s="40" t="n">
+        <v>-0.0302</v>
       </c>
       <c r="G108" s="20" t="inlineStr">
         <is>
-          <t>116.7h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H108" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28 16:00</t>
+          <t>2026-06-24 08:45</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 08:39</t>
         </is>
       </c>
     </row>
@@ -10498,40 +11560,40 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B109" s="46" t="inlineStr">
-        <is>
-          <t>WEEKLY_PRICE</t>
-        </is>
-      </c>
-      <c r="C109" s="46" t="inlineStr">
-        <is>
-          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
-        </is>
-      </c>
-      <c r="D109" s="52" t="inlineStr">
+      <c r="B109" s="43" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C109" s="43" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 5:10AM-5:15AM ET</t>
+        </is>
+      </c>
+      <c r="D109" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E109" s="47" t="n">
-        <v>0.4765</v>
-      </c>
-      <c r="F109" s="47" t="n">
-        <v>-0.08</v>
+      <c r="E109" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F109" s="44" t="n">
+        <v>-0.027</v>
       </c>
       <c r="G109" s="31" t="inlineStr">
         <is>
-          <t>92.7h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H109" s="31" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-24 09:15</t>
         </is>
       </c>
       <c r="I109" s="31" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 09:08</t>
         </is>
       </c>
     </row>
@@ -10541,40 +11603,40 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B110" s="42" t="inlineStr">
-        <is>
-          <t>WEEKLY_PRICE</t>
-        </is>
-      </c>
-      <c r="C110" s="42" t="inlineStr">
-        <is>
-          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
-        </is>
-      </c>
-      <c r="D110" s="52" t="inlineStr">
+      <c r="B110" s="39" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C110" s="39" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 5:10AM-5:15AM ET</t>
+        </is>
+      </c>
+      <c r="D110" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E110" s="43" t="n">
-        <v>0.2595</v>
-      </c>
-      <c r="F110" s="43" t="n">
-        <v>-0.1795</v>
+      <c r="E110" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F110" s="40" t="n">
+        <v>-0.1883</v>
       </c>
       <c r="G110" s="20" t="inlineStr">
         <is>
-          <t>116.7h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H110" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28 16:00</t>
+          <t>2026-06-24 09:15</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 09:08</t>
         </is>
       </c>
     </row>
@@ -10584,38 +11646,425 @@
           <t>📊 SHADOW</t>
         </is>
       </c>
-      <c r="B111" s="46" t="inlineStr">
+      <c r="B111" s="43" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C111" s="43" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 6:00AM-6:15AM ET</t>
+        </is>
+      </c>
+      <c r="D111" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="E111" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F111" s="44" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="G111" s="31" t="inlineStr">
+        <is>
+          <t>0.4h</t>
+        </is>
+      </c>
+      <c r="H111" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:15</t>
+        </is>
+      </c>
+      <c r="I111" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B112" s="39" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 6:15AM-6:20AM ET</t>
+        </is>
+      </c>
+      <c r="D112" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="E112" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F112" s="40" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="G112" s="20" t="inlineStr">
+        <is>
+          <t>0.1h</t>
+        </is>
+      </c>
+      <c r="H112" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:20</t>
+        </is>
+      </c>
+      <c r="I112" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B113" s="43" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C113" s="43" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 6:30AM-6:35AM ET</t>
+        </is>
+      </c>
+      <c r="D113" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="E113" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F113" s="44" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="G113" s="31" t="inlineStr">
+        <is>
+          <t>0.1h</t>
+        </is>
+      </c>
+      <c r="H113" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35</t>
+        </is>
+      </c>
+      <c r="I113" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B114" s="39" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C114" s="39" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 6:30AM-6:35AM ET</t>
+        </is>
+      </c>
+      <c r="D114" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E114" s="40" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="F114" s="40" t="n">
+        <v>-0.0458</v>
+      </c>
+      <c r="G114" s="20" t="inlineStr">
+        <is>
+          <t>0.1h</t>
+        </is>
+      </c>
+      <c r="H114" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35</t>
+        </is>
+      </c>
+      <c r="I114" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B115" s="43" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C115" s="43" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 6:30AM-6:35AM ET</t>
+        </is>
+      </c>
+      <c r="D115" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E115" s="44" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="F115" s="44" t="n">
+        <v>-0.0755</v>
+      </c>
+      <c r="G115" s="31" t="inlineStr">
+        <is>
+          <t>0.1h</t>
+        </is>
+      </c>
+      <c r="H115" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35</t>
+        </is>
+      </c>
+      <c r="I115" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B116" s="39" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>XRP Up or Down - June 24, 6:30AM-6:45AM ET</t>
+        </is>
+      </c>
+      <c r="D116" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E116" s="40" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F116" s="40" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="G116" s="20" t="inlineStr">
+        <is>
+          <t>0.3h</t>
+        </is>
+      </c>
+      <c r="H116" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:45</t>
+        </is>
+      </c>
+      <c r="I116" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B117" s="43" t="inlineStr">
         <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C111" s="46" t="inlineStr">
+      <c r="C117" s="43" t="inlineStr">
+        <is>
+          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
+        </is>
+      </c>
+      <c r="D117" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E117" s="44" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="F117" s="44" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="G117" s="31" t="inlineStr">
+        <is>
+          <t>116.7h</t>
+        </is>
+      </c>
+      <c r="H117" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-28 16:00</t>
+        </is>
+      </c>
+      <c r="I117" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B118" s="39" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
+        </is>
+      </c>
+      <c r="D118" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E118" s="40" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="F118" s="40" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G118" s="20" t="inlineStr">
+        <is>
+          <t>92.7h</t>
+        </is>
+      </c>
+      <c r="H118" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:00</t>
+        </is>
+      </c>
+      <c r="I118" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B119" s="43" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C119" s="43" t="inlineStr">
+        <is>
+          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
+        </is>
+      </c>
+      <c r="D119" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E119" s="44" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="F119" s="44" t="n">
+        <v>-0.1795</v>
+      </c>
+      <c r="G119" s="31" t="inlineStr">
+        <is>
+          <t>116.7h</t>
+        </is>
+      </c>
+      <c r="H119" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-28 16:00</t>
+        </is>
+      </c>
+      <c r="I119" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B120" s="39" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $90 and $100 on June 29?</t>
         </is>
       </c>
-      <c r="D111" s="52" t="inlineStr">
+      <c r="D120" s="48" t="inlineStr">
         <is>
           <t>BUY_NO</t>
         </is>
       </c>
-      <c r="E111" s="47" t="n">
+      <c r="E120" s="40" t="n">
         <v>0.473</v>
       </c>
-      <c r="F111" s="47" t="n">
+      <c r="F120" s="40" t="n">
         <v>-0.18</v>
       </c>
-      <c r="G111" s="31" t="inlineStr">
+      <c r="G120" s="20" t="inlineStr">
         <is>
           <t>140.7h</t>
         </is>
       </c>
-      <c r="H111" s="31" t="inlineStr">
+      <c r="H120" s="20" t="inlineStr">
         <is>
           <t>2026-06-29 16:00</t>
         </is>
       </c>
-      <c r="I111" s="31" t="inlineStr">
+      <c r="I120" s="20" t="inlineStr">
         <is>
           <t>2026-06-23 19:19</t>
         </is>

--- a/data/shadow/informe_bot.xlsx
+++ b/data/shadow/informe_bot.xlsx
@@ -479,7 +479,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$21:$B$102</f>
+              <f>'Dashboard'!$B$21:$B$105</f>
             </numRef>
           </val>
         </ser>
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -871,7 +871,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actualizado: 24/06/2026 10:29 UTC</t>
+          <t>Actualizado: 24/06/2026 10:38 UTC</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>35 / 47</t>
+          <t>36 / 49</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>-12.63 €</t>
+          <t>-13.60 €</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>7.37 €</t>
+          <t>6.40 €</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>❌ × 6</t>
+          <t>❌ × 2</t>
         </is>
       </c>
     </row>
@@ -1822,6 +1822,30 @@
       </c>
       <c r="B102" t="n">
         <v>7.3708</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>83</v>
+      </c>
+      <c r="B103" t="n">
+        <v>8.234999999999999</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>84</v>
+      </c>
+      <c r="B104" t="n">
+        <v>7.317</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>85</v>
+      </c>
+      <c r="B105" t="n">
+        <v>6.399</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1912,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1898,7 +1922,7 @@
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>+0.8719 €</t>
+          <t>+0.8717 €</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1934,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1932,7 +1956,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>-12.63 €</t>
+          <t>-13.60 €</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1942,7 +1966,7 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>15.28 €</t>
+          <t>16.25 €</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1978,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>-0.1540 €</t>
+          <t>-0.1600 €</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1964,7 +1988,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>-0.171</t>
+          <t>-0.178</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2000,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1986,7 +2010,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>-0.83x</t>
+          <t>-0.84x</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6719,32 +6743,188 @@
         <v>-1.02</v>
       </c>
     </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="20" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:38</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:28</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E84" s="39" t="inlineStr">
+        <is>
+          <t>Solana Up or Down - June 24, 6:30AM-6:35AM ET</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="G84" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>✅ ACIERTO</t>
+        </is>
+      </c>
+      <c r="J84" s="45" t="n">
+        <v>0.8822</v>
+      </c>
+      <c r="K84" s="45" t="n">
+        <v>0.8642</v>
+      </c>
+      <c r="L84" s="46" t="n">
+        <v>0.9602222222222222</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="31" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:38</t>
+        </is>
+      </c>
+      <c r="C85" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:28</t>
+        </is>
+      </c>
+      <c r="D85" s="31" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E85" s="43" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 6:30AM-6:35AM ET</t>
+        </is>
+      </c>
+      <c r="F85" s="31" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G85" s="44" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="H85" s="31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J85" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K85" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L85" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="20" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:38</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:28</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E86" s="39" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 6:30AM-6:35AM ET</t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G86" s="40" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J86" s="41" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K86" s="41" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="L86" s="42" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr"/>
-      <c r="C84" s="10" t="inlineStr"/>
-      <c r="D84" s="10" t="inlineStr"/>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>82 ops</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="inlineStr"/>
-      <c r="G84" s="10" t="inlineStr"/>
-      <c r="H84" s="10" t="inlineStr"/>
-      <c r="I84" s="10" t="inlineStr"/>
-      <c r="J84" s="41" t="n">
-        <v>-11.15320000000001</v>
-      </c>
-      <c r="K84" s="41" t="n">
-        <v>-12.6292</v>
-      </c>
-      <c r="L84" s="42" t="n">
-        <v>-0.1711273712737127</v>
+      <c r="B87" s="10" t="inlineStr"/>
+      <c r="C87" s="10" t="inlineStr"/>
+      <c r="D87" s="10" t="inlineStr"/>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>85 ops</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr"/>
+      <c r="G87" s="10" t="inlineStr"/>
+      <c r="H87" s="10" t="inlineStr"/>
+      <c r="I87" s="10" t="inlineStr"/>
+      <c r="J87" s="41" t="n">
+        <v>-12.07100000000001</v>
+      </c>
+      <c r="K87" s="41" t="n">
+        <v>-13.601</v>
+      </c>
+      <c r="L87" s="42" t="n">
+        <v>-0.1777908496732026</v>
       </c>
     </row>
   </sheetData>
@@ -6822,63 +7002,63 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>SMART_FLOW_1H</t>
         </is>
       </c>
       <c r="B2" s="20" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C2" s="20" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D2" s="32" t="n">
-        <v>0.4714</v>
+        <v>0.1667</v>
       </c>
       <c r="E2" s="33" t="n">
-        <v>-0.0286</v>
+        <v>-0.3333</v>
       </c>
       <c r="F2" s="33" t="n">
-        <v>-0.0639</v>
+        <v>-0.0608</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>-5.8876</v>
+        <v>-6.7416</v>
       </c>
       <c r="H2" s="23" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.5618</v>
       </c>
       <c r="I2" s="26" t="n">
-        <v>0.1597</v>
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
-          <t>SMART_FLOW_1H</t>
+          <t>UPDOWN_GBM</t>
         </is>
       </c>
       <c r="B3" s="31" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C3" s="31" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D3" s="32" t="n">
-        <v>0.1667</v>
+        <v>0.4658</v>
       </c>
       <c r="E3" s="33" t="n">
-        <v>-0.3333</v>
+        <v>-0.0342</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>-0.0608</v>
+        <v>-0.0765</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>-6.7416</v>
+        <v>-6.8594</v>
       </c>
       <c r="H3" s="23" t="n">
-        <v>-0.5618</v>
+        <v>-0.094</v>
       </c>
       <c r="I3" s="34" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1551</v>
       </c>
     </row>
   </sheetData>
@@ -6892,7 +7072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11739,33 +11919,33 @@
       </c>
       <c r="C113" s="43" t="inlineStr">
         <is>
-          <t>Solana Up or Down - June 24, 6:30AM-6:35AM ET</t>
-        </is>
-      </c>
-      <c r="D113" s="47" t="inlineStr">
-        <is>
-          <t>BUY_YES</t>
+          <t>XRP Up or Down - June 24, 6:30AM-6:45AM ET</t>
+        </is>
+      </c>
+      <c r="D113" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
         </is>
       </c>
       <c r="E113" s="44" t="n">
-        <v>0.505</v>
+        <v>0.555</v>
       </c>
       <c r="F113" s="44" t="n">
-        <v>0.0232</v>
+        <v>-0.035</v>
       </c>
       <c r="G113" s="31" t="inlineStr">
         <is>
-          <t>0.1h</t>
+          <t>0.3h</t>
         </is>
       </c>
       <c r="H113" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24 10:35</t>
+          <t>2026-06-24 10:45</t>
         </is>
       </c>
       <c r="I113" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24 10:28</t>
+          <t>2026-06-24 10:29</t>
         </is>
       </c>
     </row>
@@ -11777,12 +11957,12 @@
       </c>
       <c r="B114" s="39" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>WEEKLY_PRICE</t>
         </is>
       </c>
       <c r="C114" s="39" t="inlineStr">
         <is>
-          <t>Ethereum Up or Down - June 24, 6:30AM-6:35AM ET</t>
+          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
         </is>
       </c>
       <c r="D114" s="48" t="inlineStr">
@@ -11791,24 +11971,24 @@
         </is>
       </c>
       <c r="E114" s="40" t="n">
-        <v>0.485</v>
+        <v>0.144</v>
       </c>
       <c r="F114" s="40" t="n">
-        <v>-0.0458</v>
+        <v>-0.024</v>
       </c>
       <c r="G114" s="20" t="inlineStr">
         <is>
-          <t>0.1h</t>
+          <t>116.7h</t>
         </is>
       </c>
       <c r="H114" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24 10:35</t>
+          <t>2026-06-28 16:00</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24 10:28</t>
+          <t>2026-06-23 19:19</t>
         </is>
       </c>
     </row>
@@ -11820,12 +12000,12 @@
       </c>
       <c r="B115" s="43" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>WEEKLY_PRICE</t>
         </is>
       </c>
       <c r="C115" s="43" t="inlineStr">
         <is>
-          <t>Bitcoin Up or Down - June 24, 6:30AM-6:35AM ET</t>
+          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
         </is>
       </c>
       <c r="D115" s="48" t="inlineStr">
@@ -11834,24 +12014,24 @@
         </is>
       </c>
       <c r="E115" s="44" t="n">
-        <v>0.505</v>
+        <v>0.4765</v>
       </c>
       <c r="F115" s="44" t="n">
-        <v>-0.0755</v>
+        <v>-0.08</v>
       </c>
       <c r="G115" s="31" t="inlineStr">
         <is>
-          <t>0.1h</t>
+          <t>92.7h</t>
         </is>
       </c>
       <c r="H115" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24 10:35</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="I115" s="31" t="inlineStr">
         <is>
-          <t>2026-06-24 10:28</t>
+          <t>2026-06-23 19:19</t>
         </is>
       </c>
     </row>
@@ -11863,12 +12043,12 @@
       </c>
       <c r="B116" s="39" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>WEEKLY_PRICE</t>
         </is>
       </c>
       <c r="C116" s="39" t="inlineStr">
         <is>
-          <t>XRP Up or Down - June 24, 6:30AM-6:45AM ET</t>
+          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
         </is>
       </c>
       <c r="D116" s="48" t="inlineStr">
@@ -11877,24 +12057,24 @@
         </is>
       </c>
       <c r="E116" s="40" t="n">
-        <v>0.555</v>
+        <v>0.2595</v>
       </c>
       <c r="F116" s="40" t="n">
-        <v>-0.035</v>
+        <v>-0.1795</v>
       </c>
       <c r="G116" s="20" t="inlineStr">
         <is>
-          <t>0.3h</t>
+          <t>116.7h</t>
         </is>
       </c>
       <c r="H116" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24 10:45</t>
+          <t>2026-06-28 16:00</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24 10:29</t>
+          <t>2026-06-23 19:19</t>
         </is>
       </c>
     </row>
@@ -11911,7 +12091,7 @@
       </c>
       <c r="C117" s="43" t="inlineStr">
         <is>
-          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
+          <t>Will the price of Solana be between $90 and $100 on June 29?</t>
         </is>
       </c>
       <c r="D117" s="48" t="inlineStr">
@@ -11920,151 +12100,22 @@
         </is>
       </c>
       <c r="E117" s="44" t="n">
-        <v>0.144</v>
+        <v>0.473</v>
       </c>
       <c r="F117" s="44" t="n">
-        <v>-0.024</v>
+        <v>-0.18</v>
       </c>
       <c r="G117" s="31" t="inlineStr">
         <is>
-          <t>116.7h</t>
+          <t>140.7h</t>
         </is>
       </c>
       <c r="H117" s="31" t="inlineStr">
         <is>
-          <t>2026-06-28 16:00</t>
+          <t>2026-06-29 16:00</t>
         </is>
       </c>
       <c r="I117" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-23 19:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>📊 SHADOW</t>
-        </is>
-      </c>
-      <c r="B118" s="39" t="inlineStr">
-        <is>
-          <t>WEEKLY_PRICE</t>
-        </is>
-      </c>
-      <c r="C118" s="39" t="inlineStr">
-        <is>
-          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
-        </is>
-      </c>
-      <c r="D118" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
-        </is>
-      </c>
-      <c r="E118" s="40" t="n">
-        <v>0.4765</v>
-      </c>
-      <c r="F118" s="40" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="G118" s="20" t="inlineStr">
-        <is>
-          <t>92.7h</t>
-        </is>
-      </c>
-      <c r="H118" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-27 16:00</t>
-        </is>
-      </c>
-      <c r="I118" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-23 19:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>📊 SHADOW</t>
-        </is>
-      </c>
-      <c r="B119" s="43" t="inlineStr">
-        <is>
-          <t>WEEKLY_PRICE</t>
-        </is>
-      </c>
-      <c r="C119" s="43" t="inlineStr">
-        <is>
-          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
-        </is>
-      </c>
-      <c r="D119" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
-        </is>
-      </c>
-      <c r="E119" s="44" t="n">
-        <v>0.2595</v>
-      </c>
-      <c r="F119" s="44" t="n">
-        <v>-0.1795</v>
-      </c>
-      <c r="G119" s="31" t="inlineStr">
-        <is>
-          <t>116.7h</t>
-        </is>
-      </c>
-      <c r="H119" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-28 16:00</t>
-        </is>
-      </c>
-      <c r="I119" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-23 19:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>📊 SHADOW</t>
-        </is>
-      </c>
-      <c r="B120" s="39" t="inlineStr">
-        <is>
-          <t>WEEKLY_PRICE</t>
-        </is>
-      </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>Will the price of Solana be between $90 and $100 on June 29?</t>
-        </is>
-      </c>
-      <c r="D120" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
-        </is>
-      </c>
-      <c r="E120" s="40" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="F120" s="40" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="G120" s="20" t="inlineStr">
-        <is>
-          <t>140.7h</t>
-        </is>
-      </c>
-      <c r="H120" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:00</t>
-        </is>
-      </c>
-      <c r="I120" s="20" t="inlineStr">
         <is>
           <t>2026-06-23 19:19</t>
         </is>

--- a/data/shadow/informe_bot.xlsx
+++ b/data/shadow/informe_bot.xlsx
@@ -871,7 +871,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actualizado: 24/06/2026 18:24 UTC</t>
+          <t>Actualizado: 24/06/2026 22:05 UTC</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I405"/>
+  <dimension ref="A1:I410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39185,38 +39185,38 @@
       </c>
       <c r="B402" s="36" t="inlineStr">
         <is>
-          <t>WEEKLY_PRICE</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C402" s="36" t="inlineStr">
         <is>
-          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
-        </is>
-      </c>
-      <c r="D402" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
+          <t>XRP Up or Down - June 24, 6:05PM-6:10PM ET</t>
+        </is>
+      </c>
+      <c r="D402" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
         </is>
       </c>
       <c r="E402" s="37" t="n">
-        <v>0.144</v>
+        <v>0.5</v>
       </c>
       <c r="F402" s="37" t="n">
-        <v>-0.024</v>
+        <v>0.1921</v>
       </c>
       <c r="G402" s="19" t="inlineStr">
         <is>
-          <t>116.7h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H402" s="19" t="inlineStr">
         <is>
-          <t>2026-06-28 16:00</t>
+          <t>2026-06-24 22:10</t>
         </is>
       </c>
       <c r="I402" s="19" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 22:03</t>
         </is>
       </c>
     </row>
@@ -39228,38 +39228,38 @@
       </c>
       <c r="B403" s="40" t="inlineStr">
         <is>
-          <t>WEEKLY_PRICE</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C403" s="40" t="inlineStr">
         <is>
-          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
-        </is>
-      </c>
-      <c r="D403" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
+          <t>BNB Up or Down - June 24, 6:05PM-6:10PM ET</t>
+        </is>
+      </c>
+      <c r="D403" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
         </is>
       </c>
       <c r="E403" s="41" t="n">
-        <v>0.4765</v>
+        <v>0.5</v>
       </c>
       <c r="F403" s="41" t="n">
-        <v>-0.08</v>
+        <v>0.38</v>
       </c>
       <c r="G403" s="30" t="inlineStr">
         <is>
-          <t>92.7h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H403" s="30" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-24 22:10</t>
         </is>
       </c>
       <c r="I403" s="30" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 22:03</t>
         </is>
       </c>
     </row>
@@ -39271,38 +39271,38 @@
       </c>
       <c r="B404" s="36" t="inlineStr">
         <is>
-          <t>WEEKLY_PRICE</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C404" s="36" t="inlineStr">
         <is>
-          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
-        </is>
-      </c>
-      <c r="D404" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
+          <t>XRP Up or Down - June 24, 6:10PM-6:15PM ET</t>
+        </is>
+      </c>
+      <c r="D404" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
         </is>
       </c>
       <c r="E404" s="37" t="n">
-        <v>0.2595</v>
+        <v>0.505</v>
       </c>
       <c r="F404" s="37" t="n">
-        <v>-0.1795</v>
+        <v>0.1871</v>
       </c>
       <c r="G404" s="19" t="inlineStr">
         <is>
-          <t>116.7h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H404" s="19" t="inlineStr">
         <is>
-          <t>2026-06-28 16:00</t>
+          <t>2026-06-24 22:15</t>
         </is>
       </c>
       <c r="I404" s="19" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 22:03</t>
         </is>
       </c>
     </row>
@@ -39314,36 +39314,251 @@
       </c>
       <c r="B405" s="40" t="inlineStr">
         <is>
+          <t>ORDER_FLOW_5M</t>
+        </is>
+      </c>
+      <c r="C405" s="40" t="inlineStr">
+        <is>
+          <t>BNB Up or Down - June 24, 6:10PM-6:15PM ET</t>
+        </is>
+      </c>
+      <c r="D405" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
+        </is>
+      </c>
+      <c r="E405" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F405" s="41" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G405" s="30" t="inlineStr">
+        <is>
+          <t>0.2h</t>
+        </is>
+      </c>
+      <c r="H405" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:15</t>
+        </is>
+      </c>
+      <c r="I405" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="18" customHeight="1">
+      <c r="A406" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B406" s="36" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="C406" s="36" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 6:00PM-6:15PM ET</t>
+        </is>
+      </c>
+      <c r="D406" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E406" s="37" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="F406" s="37" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="G406" s="19" t="inlineStr">
+        <is>
+          <t>0.2h</t>
+        </is>
+      </c>
+      <c r="H406" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:15</t>
+        </is>
+      </c>
+      <c r="I406" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="18" customHeight="1">
+      <c r="A407" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B407" s="40" t="inlineStr">
+        <is>
           <t>WEEKLY_PRICE</t>
         </is>
       </c>
-      <c r="C405" s="40" t="inlineStr">
+      <c r="C407" s="40" t="inlineStr">
+        <is>
+          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
+        </is>
+      </c>
+      <c r="D407" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E407" s="41" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="F407" s="41" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="G407" s="30" t="inlineStr">
+        <is>
+          <t>116.7h</t>
+        </is>
+      </c>
+      <c r="H407" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-28 16:00</t>
+        </is>
+      </c>
+      <c r="I407" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="18" customHeight="1">
+      <c r="A408" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B408" s="36" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C408" s="36" t="inlineStr">
+        <is>
+          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
+        </is>
+      </c>
+      <c r="D408" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E408" s="37" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="F408" s="37" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G408" s="19" t="inlineStr">
+        <is>
+          <t>92.7h</t>
+        </is>
+      </c>
+      <c r="H408" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:00</t>
+        </is>
+      </c>
+      <c r="I408" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="A409" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B409" s="40" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C409" s="40" t="inlineStr">
+        <is>
+          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
+        </is>
+      </c>
+      <c r="D409" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E409" s="41" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="F409" s="41" t="n">
+        <v>-0.1795</v>
+      </c>
+      <c r="G409" s="30" t="inlineStr">
+        <is>
+          <t>116.7h</t>
+        </is>
+      </c>
+      <c r="H409" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-28 16:00</t>
+        </is>
+      </c>
+      <c r="I409" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="18" customHeight="1">
+      <c r="A410" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B410" s="36" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C410" s="36" t="inlineStr">
         <is>
           <t>Will the price of Solana be between $90 and $100 on June 29?</t>
         </is>
       </c>
-      <c r="D405" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
-        </is>
-      </c>
-      <c r="E405" s="41" t="n">
+      <c r="D410" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E410" s="37" t="n">
         <v>0.473</v>
       </c>
-      <c r="F405" s="41" t="n">
+      <c r="F410" s="37" t="n">
         <v>-0.18</v>
       </c>
-      <c r="G405" s="30" t="inlineStr">
+      <c r="G410" s="19" t="inlineStr">
         <is>
           <t>140.7h</t>
         </is>
       </c>
-      <c r="H405" s="30" t="inlineStr">
+      <c r="H410" s="19" t="inlineStr">
         <is>
           <t>2026-06-29 16:00</t>
         </is>
       </c>
-      <c r="I405" s="30" t="inlineStr">
+      <c r="I410" s="19" t="inlineStr">
         <is>
           <t>2026-06-23 19:19</t>
         </is>

--- a/data/shadow/informe_bot.xlsx
+++ b/data/shadow/informe_bot.xlsx
@@ -479,7 +479,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$21:$B$350</f>
+              <f>'Dashboard'!$B$21:$B$352</f>
             </numRef>
           </val>
         </ser>
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G350"/>
+  <dimension ref="A1:G352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -871,7 +871,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actualizado: 24/06/2026 22:05 UTC</t>
+          <t>Actualizado: 24/06/2026 23:55 UTC</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>178 / 152</t>
+          <t>178 / 154</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>+11.35 €</t>
+          <t>+10.33 €</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>+37.8%</t>
+          <t>+34.4%</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>31.35 €</t>
+          <t>30.33 €</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>❌ × 6</t>
+          <t>❌ × 8</t>
         </is>
       </c>
     </row>
@@ -3806,6 +3806,22 @@
       </c>
       <c r="B350" t="n">
         <v>31.3532</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>331</v>
+      </c>
+      <c r="B351" t="n">
+        <v>30.8432</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>332</v>
+      </c>
+      <c r="B352" t="n">
+        <v>30.3332</v>
       </c>
     </row>
   </sheetData>
@@ -3872,7 +3888,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -3894,7 +3910,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3904,7 +3920,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>-0.8486 €</t>
+          <t>-0.8442 €</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3932,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>+11.35 €</t>
+          <t>+10.33 €</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3938,7 +3954,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>+0.0344 €</t>
+          <t>+0.0311 €</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -3948,7 +3964,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>+0.041</t>
+          <t>+0.037</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3976,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -3970,7 +3986,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>0.46x</t>
+          <t>0.42x</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L332"/>
+  <dimension ref="A1:L334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21650,32 +21666,136 @@
         <v>-0.5666666666666667</v>
       </c>
     </row>
-    <row r="332" ht="22" customHeight="1">
-      <c r="A332" s="10" t="inlineStr">
+    <row r="332" ht="18" customHeight="1">
+      <c r="A332" s="19" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24 23:53</t>
+        </is>
+      </c>
+      <c r="C332" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:00</t>
+        </is>
+      </c>
+      <c r="D332" s="19" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E332" s="36" t="inlineStr">
+        <is>
+          <t>Bitcoin Up or Down - June 24, 4:00PM-8:00PM ET</t>
+        </is>
+      </c>
+      <c r="F332" s="19" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G332" s="37" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H332" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I332" s="15" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J332" s="38" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K332" s="38" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="L332" s="39" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+    </row>
+    <row r="333" ht="18" customHeight="1">
+      <c r="A333" s="30" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-24 23:53</t>
+        </is>
+      </c>
+      <c r="C333" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:00</t>
+        </is>
+      </c>
+      <c r="D333" s="30" t="inlineStr">
+        <is>
+          <t>UPDOWN_GBM</t>
+        </is>
+      </c>
+      <c r="E333" s="40" t="inlineStr">
+        <is>
+          <t>Ethereum Up or Down - June 24, 4:00PM-8:00PM ET</t>
+        </is>
+      </c>
+      <c r="F333" s="30" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="G333" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H333" s="30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I333" s="15" t="inlineStr">
+        <is>
+          <t>❌ FALLO</t>
+        </is>
+      </c>
+      <c r="J333" s="38" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K333" s="38" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="L333" s="39" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="1">
+      <c r="A334" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B332" s="10" t="inlineStr"/>
-      <c r="C332" s="10" t="inlineStr"/>
-      <c r="D332" s="10" t="inlineStr"/>
-      <c r="E332" s="10" t="inlineStr">
-        <is>
-          <t>330 ops</t>
-        </is>
-      </c>
-      <c r="F332" s="10" t="inlineStr"/>
-      <c r="G332" s="10" t="inlineStr"/>
-      <c r="H332" s="10" t="inlineStr"/>
-      <c r="I332" s="10" t="inlineStr"/>
-      <c r="J332" s="42" t="n">
-        <v>16.71080000000001</v>
-      </c>
-      <c r="K332" s="42" t="n">
-        <v>11.35320000000006</v>
-      </c>
-      <c r="L332" s="43" t="n">
-        <v>0.03822626262626282</v>
+      <c r="B334" s="10" t="inlineStr"/>
+      <c r="C334" s="10" t="inlineStr"/>
+      <c r="D334" s="10" t="inlineStr"/>
+      <c r="E334" s="10" t="inlineStr">
+        <is>
+          <t>332 ops</t>
+        </is>
+      </c>
+      <c r="F334" s="10" t="inlineStr"/>
+      <c r="G334" s="10" t="inlineStr"/>
+      <c r="H334" s="10" t="inlineStr"/>
+      <c r="I334" s="10" t="inlineStr"/>
+      <c r="J334" s="42" t="n">
+        <v>15.71080000000001</v>
+      </c>
+      <c r="K334" s="42" t="n">
+        <v>10.33320000000006</v>
+      </c>
+      <c r="L334" s="43" t="n">
+        <v>0.03458232931726927</v>
       </c>
     </row>
   </sheetData>
@@ -21788,25 +21908,25 @@
         </is>
       </c>
       <c r="B3" s="30" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" s="30" t="n">
         <v>56</v>
       </c>
       <c r="D3" s="44" t="n">
-        <v>0.5091</v>
+        <v>0.5</v>
       </c>
       <c r="E3" s="45" t="n">
-        <v>0.0091</v>
+        <v>0</v>
       </c>
       <c r="F3" s="45" t="n">
-        <v>-0.0436</v>
-      </c>
-      <c r="G3" s="46" t="n">
-        <v>0.9657</v>
-      </c>
-      <c r="H3" s="46" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0618</v>
+      </c>
+      <c r="G3" s="22" t="n">
+        <v>-0.0543</v>
+      </c>
+      <c r="H3" s="22" t="n">
+        <v>-0.0005</v>
       </c>
       <c r="I3" s="31" t="n">
         <v>0.1238</v>
@@ -21916,7 +22036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I410"/>
+  <dimension ref="A1:I412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -38669,12 +38789,12 @@
       </c>
       <c r="B390" s="36" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C390" s="36" t="inlineStr">
         <is>
-          <t>Bitcoin Up or Down - June 24, 4:00PM-8:00PM ET</t>
+          <t>BNB Up or Down - June 24, 2:10PM-2:15PM ET</t>
         </is>
       </c>
       <c r="D390" s="48" t="inlineStr">
@@ -38683,24 +38803,24 @@
         </is>
       </c>
       <c r="E390" s="37" t="n">
-        <v>0.51</v>
+        <v>0.505</v>
       </c>
       <c r="F390" s="37" t="n">
-        <v>-0.0735</v>
+        <v>-0.175</v>
       </c>
       <c r="G390" s="19" t="inlineStr">
         <is>
-          <t>6.0h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H390" s="19" t="inlineStr">
         <is>
-          <t>2026-06-25 00:00</t>
+          <t>2026-06-24 18:15</t>
         </is>
       </c>
       <c r="I390" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:00</t>
+          <t>2026-06-24 18:02</t>
         </is>
       </c>
     </row>
@@ -38712,12 +38832,12 @@
       </c>
       <c r="B391" s="40" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C391" s="40" t="inlineStr">
         <is>
-          <t>Ethereum Up or Down - June 24, 4:00PM-8:00PM ET</t>
+          <t>BNB Up or Down - June 24, 2:15PM-2:20PM ET</t>
         </is>
       </c>
       <c r="D391" s="48" t="inlineStr">
@@ -38726,24 +38846,24 @@
         </is>
       </c>
       <c r="E391" s="41" t="n">
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="F391" s="41" t="n">
-        <v>-0.1766</v>
+        <v>-0.175</v>
       </c>
       <c r="G391" s="30" t="inlineStr">
         <is>
-          <t>6.0h</t>
+          <t>0.3h</t>
         </is>
       </c>
       <c r="H391" s="30" t="inlineStr">
         <is>
-          <t>2026-06-25 00:00</t>
+          <t>2026-06-24 18:20</t>
         </is>
       </c>
       <c r="I391" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:00</t>
+          <t>2026-06-24 18:02</t>
         </is>
       </c>
     </row>
@@ -38760,7 +38880,7 @@
       </c>
       <c r="C392" s="36" t="inlineStr">
         <is>
-          <t>BNB Up or Down - June 24, 2:10PM-2:15PM ET</t>
+          <t>Dogecoin Up or Down - June 24, 2:20PM-2:25PM ET</t>
         </is>
       </c>
       <c r="D392" s="48" t="inlineStr">
@@ -38769,24 +38889,24 @@
         </is>
       </c>
       <c r="E392" s="37" t="n">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="F392" s="37" t="n">
-        <v>-0.175</v>
+        <v>-0.291</v>
       </c>
       <c r="G392" s="19" t="inlineStr">
         <is>
-          <t>0.2h</t>
+          <t>0.3h</t>
         </is>
       </c>
       <c r="H392" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:15</t>
+          <t>2026-06-24 18:25</t>
         </is>
       </c>
       <c r="I392" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:02</t>
+          <t>2026-06-24 18:05</t>
         </is>
       </c>
     </row>
@@ -38798,12 +38918,12 @@
       </c>
       <c r="B393" s="40" t="inlineStr">
         <is>
-          <t>ORDER_FLOW_5M</t>
+          <t>UPDOWN_GBM</t>
         </is>
       </c>
       <c r="C393" s="40" t="inlineStr">
         <is>
-          <t>BNB Up or Down - June 24, 2:15PM-2:20PM ET</t>
+          <t>Ethereum Up or Down - June 24, 2:15PM-2:30PM ET</t>
         </is>
       </c>
       <c r="D393" s="48" t="inlineStr">
@@ -38812,10 +38932,10 @@
         </is>
       </c>
       <c r="E393" s="41" t="n">
-        <v>0.505</v>
+        <v>0.515</v>
       </c>
       <c r="F393" s="41" t="n">
-        <v>-0.175</v>
+        <v>-0.032</v>
       </c>
       <c r="G393" s="30" t="inlineStr">
         <is>
@@ -38824,12 +38944,12 @@
       </c>
       <c r="H393" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:20</t>
+          <t>2026-06-24 18:30</t>
         </is>
       </c>
       <c r="I393" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:02</t>
+          <t>2026-06-24 18:09</t>
         </is>
       </c>
     </row>
@@ -38846,23 +38966,23 @@
       </c>
       <c r="C394" s="36" t="inlineStr">
         <is>
-          <t>Dogecoin Up or Down - June 24, 2:20PM-2:25PM ET</t>
-        </is>
-      </c>
-      <c r="D394" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
+          <t>BNB Up or Down - June 24, 2:20PM-2:25PM ET</t>
+        </is>
+      </c>
+      <c r="D394" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
         </is>
       </c>
       <c r="E394" s="37" t="n">
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="F394" s="37" t="n">
-        <v>-0.291</v>
+        <v>0.2007</v>
       </c>
       <c r="G394" s="19" t="inlineStr">
         <is>
-          <t>0.3h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H394" s="19" t="inlineStr">
@@ -38872,7 +38992,7 @@
       </c>
       <c r="I394" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:05</t>
+          <t>2026-06-24 18:11</t>
         </is>
       </c>
     </row>
@@ -38884,24 +39004,24 @@
       </c>
       <c r="B395" s="40" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C395" s="40" t="inlineStr">
         <is>
-          <t>Ethereum Up or Down - June 24, 2:15PM-2:30PM ET</t>
-        </is>
-      </c>
-      <c r="D395" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
+          <t>Dogecoin Up or Down - June 24, 2:25PM-2:30PM ET</t>
+        </is>
+      </c>
+      <c r="D395" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
         </is>
       </c>
       <c r="E395" s="41" t="n">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="F395" s="41" t="n">
-        <v>-0.032</v>
+        <v>0.2223</v>
       </c>
       <c r="G395" s="30" t="inlineStr">
         <is>
@@ -38915,7 +39035,7 @@
       </c>
       <c r="I395" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:09</t>
+          <t>2026-06-24 18:11</t>
         </is>
       </c>
     </row>
@@ -38932,7 +39052,7 @@
       </c>
       <c r="C396" s="36" t="inlineStr">
         <is>
-          <t>BNB Up or Down - June 24, 2:20PM-2:25PM ET</t>
+          <t>BNB Up or Down - June 24, 2:25PM-2:30PM ET</t>
         </is>
       </c>
       <c r="D396" s="47" t="inlineStr">
@@ -38948,12 +39068,12 @@
       </c>
       <c r="G396" s="19" t="inlineStr">
         <is>
-          <t>0.2h</t>
+          <t>0.3h</t>
         </is>
       </c>
       <c r="H396" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:25</t>
+          <t>2026-06-24 18:30</t>
         </is>
       </c>
       <c r="I396" s="19" t="inlineStr">
@@ -38975,7 +39095,7 @@
       </c>
       <c r="C397" s="40" t="inlineStr">
         <is>
-          <t>Dogecoin Up or Down - June 24, 2:25PM-2:30PM ET</t>
+          <t>XRP Up or Down - June 24, 2:25PM-2:30PM ET</t>
         </is>
       </c>
       <c r="D397" s="47" t="inlineStr">
@@ -38987,11 +39107,11 @@
         <v>0.5</v>
       </c>
       <c r="F397" s="41" t="n">
-        <v>0.2223</v>
+        <v>0.23</v>
       </c>
       <c r="G397" s="30" t="inlineStr">
         <is>
-          <t>0.3h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H397" s="30" t="inlineStr">
@@ -39001,7 +39121,7 @@
       </c>
       <c r="I397" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:11</t>
+          <t>2026-06-24 18:22</t>
         </is>
       </c>
     </row>
@@ -39018,7 +39138,7 @@
       </c>
       <c r="C398" s="36" t="inlineStr">
         <is>
-          <t>BNB Up or Down - June 24, 2:25PM-2:30PM ET</t>
+          <t>XRP Up or Down - June 24, 2:30PM-2:35PM ET</t>
         </is>
       </c>
       <c r="D398" s="47" t="inlineStr">
@@ -39030,21 +39150,21 @@
         <v>0.505</v>
       </c>
       <c r="F398" s="37" t="n">
-        <v>0.2007</v>
+        <v>0.225</v>
       </c>
       <c r="G398" s="19" t="inlineStr">
         <is>
-          <t>0.3h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H398" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:30</t>
+          <t>2026-06-24 18:35</t>
         </is>
       </c>
       <c r="I398" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:11</t>
+          <t>2026-06-24 18:22</t>
         </is>
       </c>
     </row>
@@ -39061,7 +39181,7 @@
       </c>
       <c r="C399" s="40" t="inlineStr">
         <is>
-          <t>XRP Up or Down - June 24, 2:25PM-2:30PM ET</t>
+          <t>Dogecoin Up or Down - June 24, 2:30PM-2:35PM ET</t>
         </is>
       </c>
       <c r="D399" s="47" t="inlineStr">
@@ -39073,16 +39193,16 @@
         <v>0.5</v>
       </c>
       <c r="F399" s="41" t="n">
-        <v>0.23</v>
+        <v>0.2736</v>
       </c>
       <c r="G399" s="30" t="inlineStr">
         <is>
-          <t>0.1h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H399" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:30</t>
+          <t>2026-06-24 18:35</t>
         </is>
       </c>
       <c r="I399" s="30" t="inlineStr">
@@ -39104,7 +39224,7 @@
       </c>
       <c r="C400" s="36" t="inlineStr">
         <is>
-          <t>XRP Up or Down - June 24, 2:30PM-2:35PM ET</t>
+          <t>XRP Up or Down - June 24, 6:05PM-6:10PM ET</t>
         </is>
       </c>
       <c r="D400" s="47" t="inlineStr">
@@ -39113,24 +39233,24 @@
         </is>
       </c>
       <c r="E400" s="37" t="n">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="F400" s="37" t="n">
-        <v>0.225</v>
+        <v>0.1921</v>
       </c>
       <c r="G400" s="19" t="inlineStr">
         <is>
-          <t>0.2h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H400" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:35</t>
+          <t>2026-06-24 22:10</t>
         </is>
       </c>
       <c r="I400" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:22</t>
+          <t>2026-06-24 22:03</t>
         </is>
       </c>
     </row>
@@ -39147,7 +39267,7 @@
       </c>
       <c r="C401" s="40" t="inlineStr">
         <is>
-          <t>Dogecoin Up or Down - June 24, 2:30PM-2:35PM ET</t>
+          <t>BNB Up or Down - June 24, 6:05PM-6:10PM ET</t>
         </is>
       </c>
       <c r="D401" s="47" t="inlineStr">
@@ -39159,21 +39279,21 @@
         <v>0.5</v>
       </c>
       <c r="F401" s="41" t="n">
-        <v>0.2736</v>
+        <v>0.38</v>
       </c>
       <c r="G401" s="30" t="inlineStr">
         <is>
-          <t>0.2h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H401" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:35</t>
+          <t>2026-06-24 22:10</t>
         </is>
       </c>
       <c r="I401" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 18:22</t>
+          <t>2026-06-24 22:03</t>
         </is>
       </c>
     </row>
@@ -39190,7 +39310,7 @@
       </c>
       <c r="C402" s="36" t="inlineStr">
         <is>
-          <t>XRP Up or Down - June 24, 6:05PM-6:10PM ET</t>
+          <t>XRP Up or Down - June 24, 6:10PM-6:15PM ET</t>
         </is>
       </c>
       <c r="D402" s="47" t="inlineStr">
@@ -39199,19 +39319,19 @@
         </is>
       </c>
       <c r="E402" s="37" t="n">
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="F402" s="37" t="n">
-        <v>0.1921</v>
+        <v>0.1871</v>
       </c>
       <c r="G402" s="19" t="inlineStr">
         <is>
-          <t>0.1h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H402" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 22:10</t>
+          <t>2026-06-24 22:15</t>
         </is>
       </c>
       <c r="I402" s="19" t="inlineStr">
@@ -39233,7 +39353,7 @@
       </c>
       <c r="C403" s="40" t="inlineStr">
         <is>
-          <t>BNB Up or Down - June 24, 6:05PM-6:10PM ET</t>
+          <t>BNB Up or Down - June 24, 6:10PM-6:15PM ET</t>
         </is>
       </c>
       <c r="D403" s="47" t="inlineStr">
@@ -39249,12 +39369,12 @@
       </c>
       <c r="G403" s="30" t="inlineStr">
         <is>
-          <t>0.1h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H403" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 22:10</t>
+          <t>2026-06-24 22:15</t>
         </is>
       </c>
       <c r="I403" s="30" t="inlineStr">
@@ -39271,24 +39391,24 @@
       </c>
       <c r="B404" s="36" t="inlineStr">
         <is>
-          <t>ORDER_FLOW_5M</t>
+          <t>UPDOWN_GBM</t>
         </is>
       </c>
       <c r="C404" s="36" t="inlineStr">
         <is>
-          <t>XRP Up or Down - June 24, 6:10PM-6:15PM ET</t>
-        </is>
-      </c>
-      <c r="D404" s="47" t="inlineStr">
-        <is>
-          <t>BUY_YES</t>
+          <t>Ethereum Up or Down - June 24, 6:00PM-6:15PM ET</t>
+        </is>
+      </c>
+      <c r="D404" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
         </is>
       </c>
       <c r="E404" s="37" t="n">
-        <v>0.505</v>
+        <v>0.695</v>
       </c>
       <c r="F404" s="37" t="n">
-        <v>0.1871</v>
+        <v>-0.175</v>
       </c>
       <c r="G404" s="19" t="inlineStr">
         <is>
@@ -39319,33 +39439,33 @@
       </c>
       <c r="C405" s="40" t="inlineStr">
         <is>
-          <t>BNB Up or Down - June 24, 6:10PM-6:15PM ET</t>
-        </is>
-      </c>
-      <c r="D405" s="47" t="inlineStr">
-        <is>
-          <t>BUY_YES</t>
+          <t>Ethereum Up or Down - June 24, 7:55PM-8:00PM ET</t>
+        </is>
+      </c>
+      <c r="D405" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
         </is>
       </c>
       <c r="E405" s="41" t="n">
-        <v>0.5</v>
+        <v>0.495</v>
       </c>
       <c r="F405" s="41" t="n">
-        <v>0.38</v>
+        <v>-0.324</v>
       </c>
       <c r="G405" s="30" t="inlineStr">
         <is>
-          <t>0.2h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H405" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 22:15</t>
+          <t>2026-06-25 00:00</t>
         </is>
       </c>
       <c r="I405" s="30" t="inlineStr">
         <is>
-          <t>2026-06-24 22:03</t>
+          <t>2026-06-24 23:53</t>
         </is>
       </c>
     </row>
@@ -39357,38 +39477,38 @@
       </c>
       <c r="B406" s="36" t="inlineStr">
         <is>
-          <t>UPDOWN_GBM</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C406" s="36" t="inlineStr">
         <is>
-          <t>Ethereum Up or Down - June 24, 6:00PM-6:15PM ET</t>
-        </is>
-      </c>
-      <c r="D406" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
+          <t>Dogecoin Up or Down - June 24, 7:55PM-8:00PM ET</t>
+        </is>
+      </c>
+      <c r="D406" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
         </is>
       </c>
       <c r="E406" s="37" t="n">
-        <v>0.695</v>
+        <v>0.5</v>
       </c>
       <c r="F406" s="37" t="n">
-        <v>-0.175</v>
+        <v>0.2733</v>
       </c>
       <c r="G406" s="19" t="inlineStr">
         <is>
-          <t>0.2h</t>
+          <t>0.1h</t>
         </is>
       </c>
       <c r="H406" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 22:15</t>
+          <t>2026-06-25 00:00</t>
         </is>
       </c>
       <c r="I406" s="19" t="inlineStr">
         <is>
-          <t>2026-06-24 22:03</t>
+          <t>2026-06-24 23:53</t>
         </is>
       </c>
     </row>
@@ -39400,12 +39520,12 @@
       </c>
       <c r="B407" s="40" t="inlineStr">
         <is>
-          <t>WEEKLY_PRICE</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C407" s="40" t="inlineStr">
         <is>
-          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
+          <t>Ethereum Up or Down - June 24, 8:00PM-8:05PM ET</t>
         </is>
       </c>
       <c r="D407" s="48" t="inlineStr">
@@ -39414,24 +39534,24 @@
         </is>
       </c>
       <c r="E407" s="41" t="n">
-        <v>0.144</v>
+        <v>0.495</v>
       </c>
       <c r="F407" s="41" t="n">
-        <v>-0.024</v>
+        <v>-0.324</v>
       </c>
       <c r="G407" s="30" t="inlineStr">
         <is>
-          <t>116.7h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H407" s="30" t="inlineStr">
         <is>
-          <t>2026-06-28 16:00</t>
+          <t>2026-06-25 00:05</t>
         </is>
       </c>
       <c r="I407" s="30" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 23:53</t>
         </is>
       </c>
     </row>
@@ -39443,38 +39563,38 @@
       </c>
       <c r="B408" s="36" t="inlineStr">
         <is>
-          <t>WEEKLY_PRICE</t>
+          <t>ORDER_FLOW_5M</t>
         </is>
       </c>
       <c r="C408" s="36" t="inlineStr">
         <is>
-          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
-        </is>
-      </c>
-      <c r="D408" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
+          <t>Dogecoin Up or Down - June 24, 8:00PM-8:05PM ET</t>
+        </is>
+      </c>
+      <c r="D408" s="47" t="inlineStr">
+        <is>
+          <t>BUY_YES</t>
         </is>
       </c>
       <c r="E408" s="37" t="n">
-        <v>0.4765</v>
+        <v>0.5</v>
       </c>
       <c r="F408" s="37" t="n">
-        <v>-0.08</v>
+        <v>0.2733</v>
       </c>
       <c r="G408" s="19" t="inlineStr">
         <is>
-          <t>92.7h</t>
+          <t>0.2h</t>
         </is>
       </c>
       <c r="H408" s="19" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-25 00:05</t>
         </is>
       </c>
       <c r="I408" s="19" t="inlineStr">
         <is>
-          <t>2026-06-23 19:19</t>
+          <t>2026-06-24 23:53</t>
         </is>
       </c>
     </row>
@@ -39491,7 +39611,7 @@
       </c>
       <c r="C409" s="40" t="inlineStr">
         <is>
-          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
+          <t>Will the price of Bitcoin be between $58,000 and $60,000 on June 28?</t>
         </is>
       </c>
       <c r="D409" s="48" t="inlineStr">
@@ -39500,10 +39620,10 @@
         </is>
       </c>
       <c r="E409" s="41" t="n">
-        <v>0.2595</v>
+        <v>0.144</v>
       </c>
       <c r="F409" s="41" t="n">
-        <v>-0.1795</v>
+        <v>-0.024</v>
       </c>
       <c r="G409" s="30" t="inlineStr">
         <is>
@@ -39534,31 +39654,117 @@
       </c>
       <c r="C410" s="36" t="inlineStr">
         <is>
+          <t>Will the price of Solana be between $80 and $90 on June 27?</t>
+        </is>
+      </c>
+      <c r="D410" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E410" s="37" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="F410" s="37" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G410" s="19" t="inlineStr">
+        <is>
+          <t>92.7h</t>
+        </is>
+      </c>
+      <c r="H410" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:00</t>
+        </is>
+      </c>
+      <c r="I410" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="18" customHeight="1">
+      <c r="A411" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B411" s="40" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C411" s="40" t="inlineStr">
+        <is>
+          <t>Will the price of Solana be between $90 and $100 on June 28?</t>
+        </is>
+      </c>
+      <c r="D411" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E411" s="41" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="F411" s="41" t="n">
+        <v>-0.1795</v>
+      </c>
+      <c r="G411" s="30" t="inlineStr">
+        <is>
+          <t>116.7h</t>
+        </is>
+      </c>
+      <c r="H411" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-28 16:00</t>
+        </is>
+      </c>
+      <c r="I411" s="30" t="inlineStr">
+        <is>
+          <t>2026-06-23 19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="18" customHeight="1">
+      <c r="A412" s="7" t="inlineStr">
+        <is>
+          <t>📊 SHADOW</t>
+        </is>
+      </c>
+      <c r="B412" s="36" t="inlineStr">
+        <is>
+          <t>WEEKLY_PRICE</t>
+        </is>
+      </c>
+      <c r="C412" s="36" t="inlineStr">
+        <is>
           <t>Will the price of Solana be between $90 and $100 on June 29?</t>
         </is>
       </c>
-      <c r="D410" s="48" t="inlineStr">
-        <is>
-          <t>BUY_NO</t>
-        </is>
-      </c>
-      <c r="E410" s="37" t="n">
+      <c r="D412" s="48" t="inlineStr">
+        <is>
+          <t>BUY_NO</t>
+        </is>
+      </c>
+      <c r="E412" s="37" t="n">
         <v>0.473</v>
       </c>
-      <c r="F410" s="37" t="n">
+      <c r="F412" s="37" t="n">
         <v>-0.18</v>
       </c>
-      <c r="G410" s="19" t="inlineStr">
+      <c r="G412" s="19" t="inlineStr">
         <is>
           <t>140.7h</t>
         </is>
       </c>
-      <c r="H410" s="19" t="inlineStr">
+      <c r="H412" s="19" t="inlineStr">
         <is>
           <t>2026-06-29 16:00</t>
         </is>
       </c>
-      <c r="I410" s="19" t="inlineStr">
+      <c r="I412" s="19" t="inlineStr">
         <is>
           <t>2026-06-23 19:19</t>
         </is>
